--- a/packages/calculators/src/modules/test/16-lulucf/16.2-lulucf.xlsx
+++ b/packages/calculators/src/modules/test/16-lulucf/16.2-lulucf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/16-lulucf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E074371-C6CD-6446-9CD8-39436C45866A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4CEB35-E547-B647-BB18-0F7B6D0BF159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51200" yWindow="13240" windowWidth="28800" windowHeight="27420" xr2:uid="{CC0FEAF9-C40F-694B-BCB9-117AFB86C05D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="107">
   <si>
     <t>input</t>
   </si>
@@ -833,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{851AA539-AA2F-F544-8DB9-706C333F2267}">
-  <dimension ref="A4:T178"/>
+  <dimension ref="A2:R178"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
@@ -843,28 +843,49 @@
     <col min="5" max="5" width="15.6640625" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="17.6640625" customWidth="1"/>
-    <col min="8" max="13" width="14.6640625" customWidth="1"/>
-    <col min="15" max="15" width="19.6640625" customWidth="1"/>
-    <col min="19" max="19" width="17.5" customWidth="1"/>
+    <col min="8" max="11" width="14.6640625" customWidth="1"/>
+    <col min="12" max="12" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.6640625" customWidth="1"/>
+    <col min="17" max="17" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="Q4" t="s">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="J2">
+        <f>-10*0.0041</f>
+        <v>-4.1000000000000002E-2</v>
+      </c>
+      <c r="L2">
+        <f>J2*L11</f>
+        <v>-6.4428571428571432E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="J3">
+        <f>H11*J11</f>
+        <v>-4.1000000000000007E-5</v>
+      </c>
+      <c r="L3">
+        <f>J3*L11</f>
+        <v>-6.442857142857144E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="O4" t="s">
         <v>89</v>
       </c>
-      <c r="R4">
+      <c r="P4">
         <v>4.1000000000000003E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="Q5" t="s">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="O5" t="s">
         <v>90</v>
       </c>
-      <c r="R5">
+      <c r="P5">
         <v>1.8E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>0</v>
       </c>
@@ -880,31 +901,32 @@
       <c r="G6" t="s">
         <v>1</v>
       </c>
+      <c r="J6" t="s">
+        <v>94</v>
+      </c>
+      <c r="K6" t="s">
+        <v>94</v>
+      </c>
       <c r="L6" t="s">
         <v>94</v>
       </c>
-      <c r="M6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N6" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q6" t="s">
+      <c r="O6" t="s">
         <v>91</v>
       </c>
-      <c r="R6">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="Q7" t="s">
+      <c r="P6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="O7" t="s">
         <v>92</v>
       </c>
-      <c r="R7">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="P7">
+        <f>44/28</f>
+        <v>1.5714285714285714</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D8" t="s">
         <v>106</v>
       </c>
@@ -914,15 +936,15 @@
       <c r="G8" t="s">
         <v>97</v>
       </c>
-      <c r="L8" t="s">
+      <c r="J8" t="s">
         <v>96</v>
       </c>
-      <c r="M8" t="s">
+      <c r="K8" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>100</v>
       </c>
@@ -951,25 +973,19 @@
         <v>105</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="N10" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="O10" s="5" t="s">
+      <c r="M10" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>101</v>
       </c>
@@ -977,7 +993,7 @@
         <v>5</v>
       </c>
       <c r="C11">
-        <f>VLOOKUP(B11, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B11, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.12</v>
       </c>
       <c r="D11">
@@ -988,7 +1004,7 @@
         <v>-0.18</v>
       </c>
       <c r="F11">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G11">
@@ -1004,31 +1020,23 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <f>SUM(H11:H178)</f>
-        <v>-4.574833333333336</v>
+        <f>$P$4</f>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="K11">
-        <f>SUM(I11:I178)</f>
-        <v>-42.61</v>
+        <f>$P$5</f>
+        <v>1.8E-3</v>
       </c>
       <c r="L11">
-        <f>$R$4</f>
-        <v>4.1000000000000003E-3</v>
+        <f>$P$7</f>
+        <v>1.5714285714285714</v>
       </c>
       <c r="M11">
-        <f>$R$5</f>
-        <v>1.8E-3</v>
-      </c>
-      <c r="N11">
-        <f>$R$7</f>
-        <v>1.57</v>
-      </c>
-      <c r="O11">
-        <f>(H11*$L$11+I11*$M$11)*$N$11</f>
-        <v>-6.4370000000000009E-5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+        <f>(H11*$J$11+I11*$K$11)*$L$11</f>
+        <v>-6.442857142857144E-5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>101</v>
       </c>
@@ -1036,7 +1044,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <f>VLOOKUP(B12, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B12, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.39</v>
       </c>
       <c r="D12">
@@ -1047,7 +1055,7 @@
         <v>-0.62400000000000011</v>
       </c>
       <c r="F12">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G12">
@@ -1062,12 +1070,12 @@
         <f>IF(A12="crop", 0, G12)</f>
         <v>0</v>
       </c>
-      <c r="O12">
-        <f t="shared" ref="O12:O75" si="1">(H12*$L$11+I12*$M$11)*$N$11</f>
-        <v>-2.2314933333333339E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="M12">
+        <f t="shared" ref="M12:M75" si="1">(H12*$J$11+I12*$K$11)*$L$11</f>
+        <v>-2.2335238095238101E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>101</v>
       </c>
@@ -1075,7 +1083,7 @@
         <v>7</v>
       </c>
       <c r="C13">
-        <f>VLOOKUP(B13, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B13, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.09</v>
       </c>
       <c r="D13">
@@ -1086,7 +1094,7 @@
         <v>-0.153</v>
       </c>
       <c r="F13">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G13">
@@ -1101,18 +1109,18 @@
         <f>IF(A13="crop", 0, G13)</f>
         <v>0</v>
       </c>
-      <c r="O13">
+      <c r="M13">
         <f t="shared" si="1"/>
-        <v>-5.4714500000000013E-5</v>
-      </c>
-      <c r="S13" s="6" t="s">
+        <v>-5.4764285714285726E-5</v>
+      </c>
+      <c r="Q13" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="T13" s="6">
+      <c r="R13" s="6">
         <v>-0.12</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>101</v>
       </c>
@@ -1120,7 +1128,7 @@
         <v>8</v>
       </c>
       <c r="C14">
-        <f>VLOOKUP(B14, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B14, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.09</v>
       </c>
       <c r="D14">
@@ -1131,7 +1139,7 @@
         <v>-0.16200000000000001</v>
       </c>
       <c r="F14">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G14">
@@ -1146,18 +1154,18 @@
         <f>IF(A14="crop", 0, G14)</f>
         <v>0</v>
       </c>
-      <c r="O14">
+      <c r="M14">
         <f t="shared" si="1"/>
-        <v>-5.7933000000000016E-5</v>
-      </c>
-      <c r="S14" s="6" t="s">
+        <v>-5.7985714285714297E-5</v>
+      </c>
+      <c r="Q14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="T14" s="6">
+      <c r="R14" s="6">
         <v>-0.39</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>101</v>
       </c>
@@ -1165,7 +1173,7 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <f>VLOOKUP(B15, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B15, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.13</v>
       </c>
       <c r="D15">
@@ -1176,7 +1184,7 @@
         <v>-0.247</v>
       </c>
       <c r="F15">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G15">
@@ -1191,18 +1199,18 @@
         <f>IF(A15="crop", 0, G15)</f>
         <v>0</v>
       </c>
-      <c r="O15">
+      <c r="M15">
         <f t="shared" si="1"/>
-        <v>-8.8329944444444459E-5</v>
-      </c>
-      <c r="S15" s="6" t="s">
+        <v>-8.8410317460317476E-5</v>
+      </c>
+      <c r="Q15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="T15" s="6">
+      <c r="R15" s="6">
         <v>-0.09</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>101</v>
       </c>
@@ -1210,7 +1218,7 @@
         <v>10</v>
       </c>
       <c r="C16">
-        <f>VLOOKUP(B16, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B16, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.13</v>
       </c>
       <c r="D16">
@@ -1221,7 +1229,7 @@
         <v>-0.26</v>
       </c>
       <c r="F16">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G16">
@@ -1236,18 +1244,18 @@
         <f>IF(A16="crop", 0, G16)</f>
         <v>0</v>
       </c>
-      <c r="O16">
+      <c r="M16">
         <f t="shared" si="1"/>
-        <v>-9.2978888888888917E-5</v>
-      </c>
-      <c r="S16" s="6" t="s">
+        <v>-9.3063492063492084E-5</v>
+      </c>
+      <c r="Q16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="T16" s="6">
+      <c r="R16" s="6">
         <v>-0.09</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>101</v>
       </c>
@@ -1255,7 +1263,7 @@
         <v>11</v>
       </c>
       <c r="C17">
-        <f>VLOOKUP(B17, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B17, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.55000000000000004</v>
       </c>
       <c r="D17">
@@ -1266,7 +1274,7 @@
         <v>-1.1550000000000002</v>
       </c>
       <c r="F17">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G17">
@@ -1281,18 +1289,18 @@
         <f>IF(A17="crop", 0, G17)</f>
         <v>0</v>
       </c>
-      <c r="O17">
+      <c r="M17">
         <f t="shared" si="1"/>
-        <v>-4.1304083333333343E-4</v>
-      </c>
-      <c r="S17" s="6" t="s">
+        <v>-4.1341666666666675E-4</v>
+      </c>
+      <c r="Q17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="T17" s="6">
+      <c r="R17" s="6">
         <v>-0.13</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>101</v>
       </c>
@@ -1300,7 +1308,7 @@
         <v>12</v>
       </c>
       <c r="C18">
-        <f>VLOOKUP(B18, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B18, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.01</v>
       </c>
       <c r="D18">
@@ -1311,7 +1319,7 @@
         <v>-2.2000000000000002E-2</v>
       </c>
       <c r="F18">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G18">
@@ -1326,18 +1334,18 @@
         <f>IF(A18="crop", 0, G18)</f>
         <v>0</v>
       </c>
-      <c r="O18">
+      <c r="M18">
         <f t="shared" si="1"/>
-        <v>-7.8674444444444476E-6</v>
-      </c>
-      <c r="S18" s="6" t="s">
+        <v>-7.8746031746031762E-6</v>
+      </c>
+      <c r="Q18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="T18" s="6">
+      <c r="R18" s="6">
         <v>-0.13</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>101</v>
       </c>
@@ -1345,7 +1353,7 @@
         <v>13</v>
       </c>
       <c r="C19">
-        <f>VLOOKUP(B19, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B19, $Q$13:$R$96, 2, FALSE)</f>
         <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D19">
@@ -1356,7 +1364,7 @@
         <v>-0.161</v>
       </c>
       <c r="F19">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G19">
@@ -1371,18 +1379,18 @@
         <f>IF(A19="crop", 0, G19)</f>
         <v>0</v>
       </c>
-      <c r="O19">
+      <c r="M19">
         <f t="shared" si="1"/>
-        <v>-5.7575388888888889E-5</v>
-      </c>
-      <c r="S19" s="6" t="s">
+        <v>-5.762777777777778E-5</v>
+      </c>
+      <c r="Q19" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="T19" s="6">
+      <c r="R19" s="6">
         <v>-0.55000000000000004</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>101</v>
       </c>
@@ -1390,7 +1398,7 @@
         <v>14</v>
       </c>
       <c r="C20">
-        <f>VLOOKUP(B20, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B20, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.06</v>
       </c>
       <c r="D20">
@@ -1401,7 +1409,7 @@
         <v>-0.14399999999999999</v>
       </c>
       <c r="F20">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G20">
@@ -1416,18 +1424,18 @@
         <f>IF(A20="crop", 0, G20)</f>
         <v>0</v>
       </c>
-      <c r="O20">
+      <c r="M20">
         <f t="shared" si="1"/>
-        <v>-5.149600000000001E-5</v>
-      </c>
-      <c r="S20" s="6" t="s">
+        <v>-5.1542857142857148E-5</v>
+      </c>
+      <c r="Q20" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="T20" s="6">
+      <c r="R20" s="6">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>101</v>
       </c>
@@ -1435,7 +1443,7 @@
         <v>15</v>
       </c>
       <c r="C21">
-        <f>VLOOKUP(B21, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B21, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.09</v>
       </c>
       <c r="D21">
@@ -1446,7 +1454,7 @@
         <v>-0.22499999999999998</v>
       </c>
       <c r="F21">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G21">
@@ -1461,18 +1469,18 @@
         <f>IF(A21="crop", 0, G21)</f>
         <v>0</v>
       </c>
-      <c r="O21">
+      <c r="M21">
         <f t="shared" si="1"/>
-        <v>-8.0462499999999997E-5</v>
-      </c>
-      <c r="S21" s="6" t="s">
+        <v>-8.0535714285714276E-5</v>
+      </c>
+      <c r="Q21" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="T21" s="6">
+      <c r="R21" s="6">
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>101</v>
       </c>
@@ -1480,7 +1488,7 @@
         <v>16</v>
       </c>
       <c r="C22">
-        <f>VLOOKUP(B22, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B22, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.19</v>
       </c>
       <c r="D22">
@@ -1491,7 +1499,7 @@
         <v>-0.49400000000000005</v>
       </c>
       <c r="F22">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G22">
@@ -1506,18 +1514,18 @@
         <f>IF(A22="crop", 0, G22)</f>
         <v>0</v>
       </c>
-      <c r="O22">
+      <c r="M22">
         <f t="shared" si="1"/>
-        <v>-1.7665988888888894E-4</v>
-      </c>
-      <c r="S22" s="6" t="s">
+        <v>-1.7682063492063495E-4</v>
+      </c>
+      <c r="Q22" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="T22" s="6">
+      <c r="R22" s="6">
         <v>-0.06</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>101</v>
       </c>
@@ -1525,7 +1533,7 @@
         <v>17</v>
       </c>
       <c r="C23">
-        <f>VLOOKUP(B23, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B23, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.13</v>
       </c>
       <c r="D23">
@@ -1536,7 +1544,7 @@
         <v>-0.35100000000000003</v>
       </c>
       <c r="F23">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G23">
@@ -1551,18 +1559,18 @@
         <f>IF(A23="crop", 0, G23)</f>
         <v>0</v>
       </c>
-      <c r="O23">
+      <c r="M23">
         <f t="shared" si="1"/>
-        <v>-1.2552150000000003E-4</v>
-      </c>
-      <c r="S23" s="6" t="s">
+        <v>-1.2563571428571432E-4</v>
+      </c>
+      <c r="Q23" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="T23" s="6">
+      <c r="R23" s="6">
         <v>-0.09</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>101</v>
       </c>
@@ -1570,7 +1578,7 @@
         <v>18</v>
       </c>
       <c r="C24">
-        <f>VLOOKUP(B24, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B24, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.04</v>
       </c>
       <c r="D24">
@@ -1581,7 +1589,7 @@
         <v>-0.11199999999999999</v>
       </c>
       <c r="F24">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G24">
@@ -1596,18 +1604,18 @@
         <f>IF(A24="crop", 0, G24)</f>
         <v>0</v>
       </c>
-      <c r="O24">
+      <c r="M24">
         <f t="shared" si="1"/>
-        <v>-4.0052444444444445E-5</v>
-      </c>
-      <c r="S24" s="6" t="s">
+        <v>-4.0088888888888893E-5</v>
+      </c>
+      <c r="Q24" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="T24" s="6">
+      <c r="R24" s="6">
         <v>-0.19</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>101</v>
       </c>
@@ -1615,7 +1623,7 @@
         <v>19</v>
       </c>
       <c r="C25">
-        <f>VLOOKUP(B25, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B25, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.4</v>
       </c>
       <c r="D25">
@@ -1626,7 +1634,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="F25">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G25">
@@ -1641,18 +1649,18 @@
         <f>IF(A25="crop", 0, G25)</f>
         <v>0</v>
       </c>
-      <c r="O25">
+      <c r="M25">
         <f t="shared" si="1"/>
-        <v>-4.1482888888888893E-4</v>
-      </c>
-      <c r="S25" s="6" t="s">
+        <v>-4.1520634920634922E-4</v>
+      </c>
+      <c r="Q25" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="T25" s="6">
+      <c r="R25" s="6">
         <v>-0.13</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>101</v>
       </c>
@@ -1660,7 +1668,7 @@
         <v>20</v>
       </c>
       <c r="C26">
-        <f>VLOOKUP(B26, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B26, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.09</v>
       </c>
       <c r="D26">
@@ -1671,7 +1679,7 @@
         <v>-0.27</v>
       </c>
       <c r="F26">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G26">
@@ -1686,18 +1694,18 @@
         <f>IF(A26="crop", 0, G26)</f>
         <v>0</v>
       </c>
-      <c r="O26">
+      <c r="M26">
         <f t="shared" si="1"/>
-        <v>-9.6555000000000013E-5</v>
-      </c>
-      <c r="S26" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="T26" s="6">
+        <v>-9.6642857142857153E-5</v>
+      </c>
+      <c r="Q26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R26" s="6">
         <v>-0.04</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>101</v>
       </c>
@@ -1705,7 +1713,7 @@
         <v>21</v>
       </c>
       <c r="C27">
-        <f>VLOOKUP(B27, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B27, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D27">
@@ -1716,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G27">
@@ -1731,18 +1739,18 @@
         <f>IF(A27="crop", 0, G27)</f>
         <v>0</v>
       </c>
-      <c r="O27">
+      <c r="M27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S27" s="6" t="s">
+      <c r="Q27" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="T27" s="6">
+      <c r="R27" s="6">
         <v>-0.4</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>101</v>
       </c>
@@ -1750,7 +1758,7 @@
         <v>22</v>
       </c>
       <c r="C28">
-        <f>VLOOKUP(B28, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B28, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.44</v>
       </c>
       <c r="D28">
@@ -1761,7 +1769,7 @@
         <v>-1.4080000000000001</v>
       </c>
       <c r="F28">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G28">
@@ -1776,18 +1784,18 @@
         <f>IF(A28="crop", 0, G28)</f>
         <v>0</v>
       </c>
-      <c r="O28">
+      <c r="M28">
         <f t="shared" si="1"/>
-        <v>-5.0351644444444465E-4</v>
-      </c>
-      <c r="S28" s="6" t="s">
+        <v>-5.0397460317460328E-4</v>
+      </c>
+      <c r="Q28" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="T28" s="6">
+      <c r="R28" s="6">
         <v>-0.09</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>101</v>
       </c>
@@ -1795,7 +1803,7 @@
         <v>23</v>
       </c>
       <c r="C29">
-        <f>VLOOKUP(B29, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B29, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.21</v>
       </c>
       <c r="D29">
@@ -1806,7 +1814,7 @@
         <v>-0.69299999999999995</v>
       </c>
       <c r="F29">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G29">
@@ -1821,18 +1829,18 @@
         <f>IF(A29="crop", 0, G29)</f>
         <v>0</v>
       </c>
-      <c r="O29">
+      <c r="M29">
         <f t="shared" si="1"/>
-        <v>-2.4782450000000001E-4</v>
-      </c>
-      <c r="S29" s="6" t="s">
+        <v>-2.4805000000000004E-4</v>
+      </c>
+      <c r="Q29" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="T29" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="R29" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>101</v>
       </c>
@@ -1840,7 +1848,7 @@
         <v>24</v>
       </c>
       <c r="C30">
-        <f>VLOOKUP(B30, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B30, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.21</v>
       </c>
       <c r="D30">
@@ -1851,7 +1859,7 @@
         <v>-0.71399999999999997</v>
       </c>
       <c r="F30">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G30">
@@ -1866,18 +1874,18 @@
         <f>IF(A30="crop", 0, G30)</f>
         <v>0</v>
       </c>
-      <c r="O30">
+      <c r="M30">
         <f t="shared" si="1"/>
-        <v>-2.5533433333333334E-4</v>
-      </c>
-      <c r="S30" s="6" t="s">
+        <v>-2.5556666666666663E-4</v>
+      </c>
+      <c r="Q30" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="T30" s="6">
+      <c r="R30" s="6">
         <v>-0.44</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>101</v>
       </c>
@@ -1885,7 +1893,7 @@
         <v>25</v>
       </c>
       <c r="C31">
-        <f>VLOOKUP(B31, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B31, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D31">
@@ -1896,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G31">
@@ -1911,18 +1919,18 @@
         <f>IF(A31="crop", 0, G31)</f>
         <v>0</v>
       </c>
-      <c r="O31">
+      <c r="M31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S31" s="6" t="s">
+      <c r="Q31" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="T31" s="6">
+      <c r="R31" s="6">
         <v>-0.21</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>101</v>
       </c>
@@ -1930,7 +1938,7 @@
         <v>26</v>
       </c>
       <c r="C32">
-        <f>VLOOKUP(B32, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B32, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.04</v>
       </c>
       <c r="D32">
@@ -1941,7 +1949,7 @@
         <v>-0.14400000000000002</v>
       </c>
       <c r="F32">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G32">
@@ -1956,18 +1964,18 @@
         <f>IF(A32="crop", 0, G32)</f>
         <v>0</v>
       </c>
-      <c r="O32">
+      <c r="M32">
         <f t="shared" si="1"/>
-        <v>-5.149600000000001E-5</v>
-      </c>
-      <c r="S32" s="6" t="s">
+        <v>-5.1542857142857148E-5</v>
+      </c>
+      <c r="Q32" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="T32" s="6">
+      <c r="R32" s="6">
         <v>-0.21</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>101</v>
       </c>
@@ -1975,7 +1983,7 @@
         <v>27</v>
       </c>
       <c r="C33">
-        <f>VLOOKUP(B33, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B33, $Q$13:$R$96, 2, FALSE)</f>
         <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D33">
@@ -1986,7 +1994,7 @@
         <v>-0.25900000000000006</v>
       </c>
       <c r="F33">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G33">
@@ -2001,18 +2009,18 @@
         <f>IF(A33="crop", 0, G33)</f>
         <v>0</v>
       </c>
-      <c r="O33">
+      <c r="M33">
         <f t="shared" si="1"/>
-        <v>-9.262127777777781E-5</v>
-      </c>
-      <c r="S33" s="6" t="s">
+        <v>-9.270555555555558E-5</v>
+      </c>
+      <c r="Q33" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="T33" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="R33" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>101</v>
       </c>
@@ -2020,7 +2028,7 @@
         <v>28</v>
       </c>
       <c r="C34">
-        <f>VLOOKUP(B34, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B34, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.04</v>
       </c>
       <c r="D34">
@@ -2031,7 +2039,7 @@
         <v>-0.152</v>
       </c>
       <c r="F34">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G34">
@@ -2046,18 +2054,18 @@
         <f>IF(A34="crop", 0, G34)</f>
         <v>0</v>
       </c>
-      <c r="O34">
+      <c r="M34">
         <f t="shared" si="1"/>
-        <v>-5.4356888888888886E-5</v>
-      </c>
-      <c r="S34" s="6" t="s">
+        <v>-5.4406349206349202E-5</v>
+      </c>
+      <c r="Q34" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="T34" s="6">
+      <c r="R34" s="6">
         <v>-0.04</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>101</v>
       </c>
@@ -2065,7 +2073,7 @@
         <v>29</v>
       </c>
       <c r="C35">
-        <f>VLOOKUP(B35, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B35, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.24</v>
       </c>
       <c r="D35">
@@ -2076,7 +2084,7 @@
         <v>-0.93599999999999994</v>
       </c>
       <c r="F35">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G35">
@@ -2091,18 +2099,18 @@
         <f>IF(A35="crop", 0, G35)</f>
         <v>0</v>
       </c>
-      <c r="O35">
+      <c r="M35">
         <f t="shared" si="1"/>
-        <v>-3.34724E-4</v>
-      </c>
-      <c r="S35" s="6" t="s">
+        <v>-3.3502857142857142E-4</v>
+      </c>
+      <c r="Q35" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="T35" s="6">
+      <c r="R35" s="6">
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>101</v>
       </c>
@@ -2110,7 +2118,7 @@
         <v>30</v>
       </c>
       <c r="C36">
-        <f>VLOOKUP(B36, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B36, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.17</v>
       </c>
       <c r="D36">
@@ -2121,7 +2129,7 @@
         <v>-0.68</v>
       </c>
       <c r="F36">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G36">
@@ -2136,18 +2144,18 @@
         <f>IF(A36="crop", 0, G36)</f>
         <v>0</v>
       </c>
-      <c r="O36">
+      <c r="M36">
         <f t="shared" si="1"/>
-        <v>-2.4317555555555557E-4</v>
-      </c>
-      <c r="S36" s="6" t="s">
+        <v>-2.433968253968254E-4</v>
+      </c>
+      <c r="Q36" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="T36" s="6">
+      <c r="R36" s="6">
         <v>-0.04</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>101</v>
       </c>
@@ -2155,7 +2163,7 @@
         <v>31</v>
       </c>
       <c r="C37">
-        <f>VLOOKUP(B37, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B37, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.03</v>
       </c>
       <c r="D37">
@@ -2166,7 +2174,7 @@
         <v>-0.12299999999999998</v>
       </c>
       <c r="F37">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G37">
@@ -2181,18 +2189,18 @@
         <f>IF(A37="crop", 0, G37)</f>
         <v>0</v>
       </c>
-      <c r="O37">
+      <c r="M37">
         <f t="shared" si="1"/>
-        <v>-4.3986166666666669E-5</v>
-      </c>
-      <c r="S37" s="6" t="s">
+        <v>-4.4026190476190472E-5</v>
+      </c>
+      <c r="Q37" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="T37" s="6">
+      <c r="R37" s="6">
         <v>-0.24</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>101</v>
       </c>
@@ -2200,7 +2208,7 @@
         <v>32</v>
       </c>
       <c r="C38">
-        <f>VLOOKUP(B38, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B38, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.02</v>
       </c>
       <c r="D38">
@@ -2211,7 +2219,7 @@
         <v>-8.4000000000000005E-2</v>
       </c>
       <c r="F38">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G38">
@@ -2226,18 +2234,18 @@
         <f>IF(A38="crop", 0, G38)</f>
         <v>0</v>
       </c>
-      <c r="O38">
+      <c r="M38">
         <f t="shared" si="1"/>
-        <v>-3.0039333333333339E-5</v>
-      </c>
-      <c r="S38" s="6" t="s">
+        <v>-3.0066666666666668E-5</v>
+      </c>
+      <c r="Q38" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="T38" s="6">
+      <c r="R38" s="6">
         <v>-0.17</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>101</v>
       </c>
@@ -2245,7 +2253,7 @@
         <v>33</v>
       </c>
       <c r="C39">
-        <f>VLOOKUP(B39, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B39, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.43</v>
       </c>
       <c r="D39">
@@ -2256,7 +2264,7 @@
         <v>-1.849</v>
       </c>
       <c r="F39">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G39">
@@ -2271,18 +2279,18 @@
         <f>IF(A39="crop", 0, G39)</f>
         <v>0</v>
       </c>
-      <c r="O39">
+      <c r="M39">
         <f t="shared" si="1"/>
-        <v>-6.6122294444444446E-4</v>
-      </c>
-      <c r="S39" s="6" t="s">
+        <v>-6.6182460317460313E-4</v>
+      </c>
+      <c r="Q39" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="T39" s="6">
+      <c r="R39" s="6">
         <v>-0.03</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>101</v>
       </c>
@@ -2290,7 +2298,7 @@
         <v>34</v>
       </c>
       <c r="C40">
-        <f>VLOOKUP(B40, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B40, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.14000000000000001</v>
       </c>
       <c r="D40">
@@ -2301,7 +2309,7 @@
         <v>-0.6160000000000001</v>
       </c>
       <c r="F40">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G40">
@@ -2316,18 +2324,18 @@
         <f>IF(A40="crop", 0, G40)</f>
         <v>0</v>
       </c>
-      <c r="O40">
+      <c r="M40">
         <f t="shared" si="1"/>
-        <v>-2.2028844444444451E-4</v>
-      </c>
-      <c r="S40" s="6" t="s">
+        <v>-2.2048888888888895E-4</v>
+      </c>
+      <c r="Q40" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="T40" s="6">
+      <c r="R40" s="6">
         <v>-0.02</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>101</v>
       </c>
@@ -2335,7 +2343,7 @@
         <v>35</v>
       </c>
       <c r="C41">
-        <f>VLOOKUP(B41, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B41, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D41">
@@ -2346,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G41">
@@ -2361,18 +2369,18 @@
         <f>IF(A41="crop", 0, G41)</f>
         <v>0</v>
       </c>
-      <c r="O41">
+      <c r="M41">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S41" s="6" t="s">
+      <c r="Q41" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="T41" s="6">
+      <c r="R41" s="6">
         <v>-0.43</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>101</v>
       </c>
@@ -2380,7 +2388,7 @@
         <v>36</v>
       </c>
       <c r="C42">
-        <f>VLOOKUP(B42, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B42, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.12</v>
       </c>
       <c r="D42">
@@ -2391,7 +2399,7 @@
         <v>-0.55199999999999994</v>
       </c>
       <c r="F42">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G42">
@@ -2406,18 +2414,18 @@
         <f>IF(A42="crop", 0, G42)</f>
         <v>0</v>
       </c>
-      <c r="O42">
+      <c r="M42">
         <f t="shared" si="1"/>
-        <v>-1.9740133333333331E-4</v>
-      </c>
-      <c r="S42" s="6" t="s">
+        <v>-1.9758095238095236E-4</v>
+      </c>
+      <c r="Q42" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="T42" s="6">
+      <c r="R42" s="6">
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>101</v>
       </c>
@@ -2425,7 +2433,7 @@
         <v>37</v>
       </c>
       <c r="C43">
-        <f>VLOOKUP(B43, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B43, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.13</v>
       </c>
       <c r="D43">
@@ -2436,7 +2444,7 @@
         <v>-0.6110000000000001</v>
       </c>
       <c r="F43">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G43">
@@ -2451,18 +2459,18 @@
         <f>IF(A43="crop", 0, G43)</f>
         <v>0</v>
       </c>
-      <c r="O43">
+      <c r="M43">
         <f t="shared" si="1"/>
-        <v>-2.1850038888888894E-4</v>
-      </c>
-      <c r="S43" s="6" t="s">
+        <v>-2.1869920634920637E-4</v>
+      </c>
+      <c r="Q43" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="T43" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="R43" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>101</v>
       </c>
@@ -2470,7 +2478,7 @@
         <v>38</v>
       </c>
       <c r="C44">
-        <f>VLOOKUP(B44, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B44, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.16</v>
       </c>
       <c r="D44">
@@ -2481,7 +2489,7 @@
         <v>-0.76800000000000002</v>
       </c>
       <c r="F44">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G44">
@@ -2496,18 +2504,18 @@
         <f>IF(A44="crop", 0, G44)</f>
         <v>0</v>
       </c>
-      <c r="O44">
+      <c r="M44">
         <f t="shared" si="1"/>
-        <v>-2.7464533333333339E-4</v>
-      </c>
-      <c r="S44" s="6" t="s">
+        <v>-2.7489523809523812E-4</v>
+      </c>
+      <c r="Q44" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="T44" s="6">
+      <c r="R44" s="6">
         <v>-0.12</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>101</v>
       </c>
@@ -2515,7 +2523,7 @@
         <v>39</v>
       </c>
       <c r="C45">
-        <f>VLOOKUP(B45, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B45, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.09</v>
       </c>
       <c r="D45">
@@ -2526,7 +2534,7 @@
         <v>-0.441</v>
       </c>
       <c r="F45">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G45">
@@ -2541,18 +2549,18 @@
         <f>IF(A45="crop", 0, G45)</f>
         <v>0</v>
       </c>
-      <c r="O45">
+      <c r="M45">
         <f t="shared" si="1"/>
-        <v>-1.5770650000000003E-4</v>
-      </c>
-      <c r="S45" s="6" t="s">
+        <v>-1.5785000000000002E-4</v>
+      </c>
+      <c r="Q45" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="T45" s="6">
+      <c r="R45" s="6">
         <v>-0.13</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -2560,7 +2568,7 @@
         <v>40</v>
       </c>
       <c r="C46">
-        <f>VLOOKUP(B46, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B46, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D46">
@@ -2571,7 +2579,7 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G46">
@@ -2586,18 +2594,18 @@
         <f>IF(A46="crop", 0, G46)</f>
         <v>0</v>
       </c>
-      <c r="O46">
+      <c r="M46">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S46" s="6" t="s">
+      <c r="Q46" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="T46" s="6">
+      <c r="R46" s="6">
         <v>-0.16</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>101</v>
       </c>
@@ -2605,7 +2613,7 @@
         <v>41</v>
       </c>
       <c r="C47">
-        <f>VLOOKUP(B47, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B47, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.04</v>
       </c>
       <c r="D47">
@@ -2616,7 +2624,7 @@
         <v>-0.20399999999999999</v>
       </c>
       <c r="F47">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G47">
@@ -2631,18 +2639,18 @@
         <f>IF(A47="crop", 0, G47)</f>
         <v>0</v>
       </c>
-      <c r="O47">
+      <c r="M47">
         <f t="shared" si="1"/>
-        <v>-7.295266666666667E-5</v>
-      </c>
-      <c r="S47" s="6" t="s">
+        <v>-7.3019047619047621E-5</v>
+      </c>
+      <c r="Q47" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="T47" s="6">
+      <c r="R47" s="6">
         <v>-0.09</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>101</v>
       </c>
@@ -2650,7 +2658,7 @@
         <v>42</v>
       </c>
       <c r="C48">
-        <f>VLOOKUP(B48, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B48, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.03</v>
       </c>
       <c r="D48">
@@ -2661,7 +2669,7 @@
         <v>-0.156</v>
       </c>
       <c r="F48">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G48">
@@ -2676,18 +2684,18 @@
         <f>IF(A48="crop", 0, G48)</f>
         <v>0</v>
       </c>
-      <c r="O48">
+      <c r="M48">
         <f t="shared" si="1"/>
-        <v>-5.5787333333333334E-5</v>
-      </c>
-      <c r="S48" s="6" t="s">
+        <v>-5.5838095238095238E-5</v>
+      </c>
+      <c r="Q48" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="T48" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="R48" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>101</v>
       </c>
@@ -2695,7 +2703,7 @@
         <v>43</v>
       </c>
       <c r="C49">
-        <f>VLOOKUP(B49, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B49, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.14000000000000001</v>
       </c>
       <c r="D49">
@@ -2706,7 +2714,7 @@
         <v>-0.74199999999999999</v>
       </c>
       <c r="F49">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G49">
@@ -2721,18 +2729,18 @@
         <f>IF(A49="crop", 0, G49)</f>
         <v>0</v>
       </c>
-      <c r="O49">
+      <c r="M49">
         <f t="shared" si="1"/>
-        <v>-2.6534744444444444E-4</v>
-      </c>
-      <c r="S49" s="6" t="s">
+        <v>-2.6558888888888891E-4</v>
+      </c>
+      <c r="Q49" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="T49" s="6">
+      <c r="R49" s="6">
         <v>-0.04</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>101</v>
       </c>
@@ -2740,7 +2748,7 @@
         <v>44</v>
       </c>
       <c r="C50">
-        <f>VLOOKUP(B50, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B50, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.31</v>
       </c>
       <c r="D50">
@@ -2751,7 +2759,7 @@
         <v>-1.6740000000000002</v>
       </c>
       <c r="F50">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G50">
@@ -2766,18 +2774,18 @@
         <f>IF(A50="crop", 0, G50)</f>
         <v>0</v>
       </c>
-      <c r="O50">
+      <c r="M50">
         <f t="shared" si="1"/>
-        <v>-5.9864100000000023E-4</v>
-      </c>
-      <c r="S50" s="6" t="s">
+        <v>-5.9918571428571447E-4</v>
+      </c>
+      <c r="Q50" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="T50" s="6">
+      <c r="R50" s="6">
         <v>-0.03</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -2785,7 +2793,7 @@
         <v>45</v>
       </c>
       <c r="C51">
-        <f>VLOOKUP(B51, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B51, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.23</v>
       </c>
       <c r="D51">
@@ -2796,7 +2804,7 @@
         <v>-1.2650000000000001</v>
       </c>
       <c r="F51">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G51">
@@ -2811,18 +2819,18 @@
         <f>IF(A51="crop", 0, G51)</f>
         <v>0</v>
       </c>
-      <c r="O51">
+      <c r="M51">
         <f t="shared" si="1"/>
-        <v>-4.5237805555555568E-4</v>
-      </c>
-      <c r="S51" s="6" t="s">
+        <v>-4.5278968253968259E-4</v>
+      </c>
+      <c r="Q51" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="T51" s="6">
+      <c r="R51" s="6">
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>101</v>
       </c>
@@ -2830,7 +2838,7 @@
         <v>46</v>
       </c>
       <c r="C52">
-        <f>VLOOKUP(B52, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B52, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.17</v>
       </c>
       <c r="D52">
@@ -2841,7 +2849,7 @@
         <v>-0.95199999999999996</v>
       </c>
       <c r="F52">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G52">
@@ -2856,18 +2864,18 @@
         <f>IF(A52="crop", 0, G52)</f>
         <v>0</v>
       </c>
-      <c r="O52">
+      <c r="M52">
         <f t="shared" si="1"/>
-        <v>-3.4044577777777782E-4</v>
-      </c>
-      <c r="S52" s="6" t="s">
+        <v>-3.4075555555555559E-4</v>
+      </c>
+      <c r="Q52" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="T52" s="6">
+      <c r="R52" s="6">
         <v>-0.31</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>101</v>
       </c>
@@ -2875,7 +2883,7 @@
         <v>47</v>
       </c>
       <c r="C53">
-        <f>VLOOKUP(B53, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B53, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.17</v>
       </c>
       <c r="D53">
@@ -2886,7 +2894,7 @@
         <v>-0.96900000000000008</v>
       </c>
       <c r="F53">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G53">
@@ -2901,18 +2909,18 @@
         <f>IF(A53="crop", 0, G53)</f>
         <v>0</v>
       </c>
-      <c r="O53">
+      <c r="M53">
         <f t="shared" si="1"/>
-        <v>-3.4652516666666672E-4</v>
-      </c>
-      <c r="S53" s="6" t="s">
+        <v>-3.4684047619047622E-4</v>
+      </c>
+      <c r="Q53" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="T53" s="6">
+      <c r="R53" s="6">
         <v>-0.23</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>101</v>
       </c>
@@ -2920,7 +2928,7 @@
         <v>48</v>
       </c>
       <c r="C54">
-        <f>VLOOKUP(B54, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B54, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.08</v>
       </c>
       <c r="D54">
@@ -2931,7 +2939,7 @@
         <v>-0.46399999999999997</v>
       </c>
       <c r="F54">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G54">
@@ -2946,18 +2954,18 @@
         <f>IF(A54="crop", 0, G54)</f>
         <v>0</v>
       </c>
-      <c r="O54">
+      <c r="M54">
         <f t="shared" si="1"/>
-        <v>-1.6593155555555555E-4</v>
-      </c>
-      <c r="S54" s="6" t="s">
+        <v>-1.6608253968253966E-4</v>
+      </c>
+      <c r="Q54" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="T54" s="6">
+      <c r="R54" s="6">
         <v>-0.17</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>101</v>
       </c>
@@ -2965,7 +2973,7 @@
         <v>49</v>
       </c>
       <c r="C55">
-        <f>VLOOKUP(B55, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B55, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.11</v>
       </c>
       <c r="D55">
@@ -2976,7 +2984,7 @@
         <v>-0.64900000000000002</v>
       </c>
       <c r="F55">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G55">
@@ -2991,18 +2999,18 @@
         <f>IF(A55="crop", 0, G55)</f>
         <v>0</v>
       </c>
-      <c r="O55">
+      <c r="M55">
         <f t="shared" si="1"/>
-        <v>-2.3208961111111114E-4</v>
-      </c>
-      <c r="S55" s="6" t="s">
+        <v>-2.3230079365079367E-4</v>
+      </c>
+      <c r="Q55" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="T55" s="6">
+      <c r="R55" s="6">
         <v>-0.17</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>101</v>
       </c>
@@ -3010,7 +3018,7 @@
         <v>50</v>
       </c>
       <c r="C56">
-        <f>VLOOKUP(B56, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B56, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D56">
@@ -3021,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="F56">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G56">
@@ -3036,18 +3044,18 @@
         <f>IF(A56="crop", 0, G56)</f>
         <v>0</v>
       </c>
-      <c r="O56">
+      <c r="M56">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S56" s="6" t="s">
+      <c r="Q56" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="T56" s="6">
+      <c r="R56" s="6">
         <v>-0.08</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>101</v>
       </c>
@@ -3055,7 +3063,7 @@
         <v>51</v>
       </c>
       <c r="C57">
-        <f>VLOOKUP(B57, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B57, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.02</v>
       </c>
       <c r="D57">
@@ -3066,7 +3074,7 @@
         <v>-0.122</v>
       </c>
       <c r="F57">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G57">
@@ -3081,18 +3089,18 @@
         <f>IF(A57="crop", 0, G57)</f>
         <v>0</v>
       </c>
-      <c r="O57">
+      <c r="M57">
         <f t="shared" si="1"/>
-        <v>-4.3628555555555555E-5</v>
-      </c>
-      <c r="S57" s="6" t="s">
+        <v>-4.3668253968253968E-5</v>
+      </c>
+      <c r="Q57" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="T57" s="6">
+      <c r="R57" s="6">
         <v>-0.11</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>101</v>
       </c>
@@ -3100,7 +3108,7 @@
         <v>52</v>
       </c>
       <c r="C58">
-        <f>VLOOKUP(B58, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B58, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.08</v>
       </c>
       <c r="D58">
@@ -3111,7 +3119,7 @@
         <v>-0.49600000000000005</v>
       </c>
       <c r="F58">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G58">
@@ -3126,18 +3134,18 @@
         <f>IF(A58="crop", 0, G58)</f>
         <v>0</v>
       </c>
-      <c r="O58">
+      <c r="M58">
         <f t="shared" si="1"/>
-        <v>-1.7737511111111116E-4</v>
-      </c>
-      <c r="S58" s="6" t="s">
+        <v>-1.7753650793650796E-4</v>
+      </c>
+      <c r="Q58" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="T58" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="R58" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>101</v>
       </c>
@@ -3145,7 +3153,7 @@
         <v>53</v>
       </c>
       <c r="C59">
-        <f>VLOOKUP(B59, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B59, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.06</v>
       </c>
       <c r="D59">
@@ -3156,7 +3164,7 @@
         <v>-0.378</v>
       </c>
       <c r="F59">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G59">
@@ -3171,18 +3179,18 @@
         <f>IF(A59="crop", 0, G59)</f>
         <v>0</v>
       </c>
-      <c r="O59">
+      <c r="M59">
         <f t="shared" si="1"/>
-        <v>-1.3517700000000002E-4</v>
-      </c>
-      <c r="S59" s="6" t="s">
+        <v>-1.3530000000000004E-4</v>
+      </c>
+      <c r="Q59" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="T59" s="6">
+      <c r="R59" s="6">
         <v>-0.02</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>101</v>
       </c>
@@ -3190,7 +3198,7 @@
         <v>54</v>
       </c>
       <c r="C60">
-        <f>VLOOKUP(B60, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B60, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.12</v>
       </c>
       <c r="D60">
@@ -3201,7 +3209,7 @@
         <v>-0.76800000000000002</v>
       </c>
       <c r="F60">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G60">
@@ -3216,18 +3224,18 @@
         <f>IF(A60="crop", 0, G60)</f>
         <v>0</v>
       </c>
-      <c r="O60">
+      <c r="M60">
         <f t="shared" si="1"/>
-        <v>-2.7464533333333339E-4</v>
-      </c>
-      <c r="S60" s="6" t="s">
+        <v>-2.7489523809523812E-4</v>
+      </c>
+      <c r="Q60" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="T60" s="6">
+      <c r="R60" s="6">
         <v>-0.08</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>101</v>
       </c>
@@ -3235,7 +3243,7 @@
         <v>55</v>
       </c>
       <c r="C61">
-        <f>VLOOKUP(B61, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B61, $Q$13:$R$96, 2, FALSE)</f>
         <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D61">
@@ -3246,7 +3254,7 @@
         <v>-0.45500000000000007</v>
       </c>
       <c r="F61">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G61">
@@ -3261,18 +3269,18 @@
         <f>IF(A61="crop", 0, G61)</f>
         <v>0</v>
       </c>
-      <c r="O61">
+      <c r="M61">
         <f t="shared" si="1"/>
-        <v>-1.6271305555555561E-4</v>
-      </c>
-      <c r="S61" s="6" t="s">
+        <v>-1.6286111111111115E-4</v>
+      </c>
+      <c r="Q61" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="T61" s="6">
+      <c r="R61" s="6">
         <v>-0.06</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>101</v>
       </c>
@@ -3280,7 +3288,7 @@
         <v>56</v>
       </c>
       <c r="C62">
-        <f>VLOOKUP(B62, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B62, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.13</v>
       </c>
       <c r="D62">
@@ -3291,7 +3299,7 @@
         <v>-0.85799999999999998</v>
       </c>
       <c r="F62">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G62">
@@ -3306,18 +3314,18 @@
         <f>IF(A62="crop", 0, G62)</f>
         <v>0</v>
       </c>
-      <c r="O62">
+      <c r="M62">
         <f t="shared" si="1"/>
-        <v>-3.0683033333333334E-4</v>
-      </c>
-      <c r="S62" s="6" t="s">
+        <v>-3.0710952380952382E-4</v>
+      </c>
+      <c r="Q62" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="T62" s="6">
+      <c r="R62" s="6">
         <v>-0.12</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>101</v>
       </c>
@@ -3325,7 +3333,7 @@
         <v>57</v>
       </c>
       <c r="C63">
-        <f>VLOOKUP(B63, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B63, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D63">
@@ -3336,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="F63">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G63">
@@ -3351,18 +3359,18 @@
         <f>IF(A63="crop", 0, G63)</f>
         <v>0</v>
       </c>
-      <c r="O63">
+      <c r="M63">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S63" s="6" t="s">
+      <c r="Q63" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="T63" s="6">
+      <c r="R63" s="6">
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>101</v>
       </c>
@@ -3370,7 +3378,7 @@
         <v>58</v>
       </c>
       <c r="C64">
-        <f>VLOOKUP(B64, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B64, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.24</v>
       </c>
       <c r="D64">
@@ -3381,7 +3389,7 @@
         <v>-1.6319999999999999</v>
       </c>
       <c r="F64">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G64">
@@ -3396,18 +3404,18 @@
         <f>IF(A64="crop", 0, G64)</f>
         <v>0</v>
       </c>
-      <c r="O64">
+      <c r="M64">
         <f t="shared" si="1"/>
-        <v>-5.8362133333333336E-4</v>
-      </c>
-      <c r="S64" s="6" t="s">
+        <v>-5.8415238095238097E-4</v>
+      </c>
+      <c r="Q64" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="T64" s="6">
+      <c r="R64" s="6">
         <v>-0.13</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>101</v>
       </c>
@@ -3415,7 +3423,7 @@
         <v>59</v>
       </c>
       <c r="C65">
-        <f>VLOOKUP(B65, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B65, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.32</v>
       </c>
       <c r="D65">
@@ -3426,7 +3434,7 @@
         <v>-2.2080000000000002</v>
       </c>
       <c r="F65">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G65">
@@ -3441,18 +3449,18 @@
         <f>IF(A65="crop", 0, G65)</f>
         <v>0</v>
       </c>
-      <c r="O65">
+      <c r="M65">
         <f t="shared" si="1"/>
-        <v>-7.8960533333333346E-4</v>
-      </c>
-      <c r="S65" s="6" t="s">
+        <v>-7.9032380952380953E-4</v>
+      </c>
+      <c r="Q65" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="T65" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="R65" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>101</v>
       </c>
@@ -3460,7 +3468,7 @@
         <v>60</v>
       </c>
       <c r="C66">
-        <f>VLOOKUP(B66, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B66, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D66">
@@ -3471,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="F66">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G66">
@@ -3486,18 +3494,18 @@
         <f>IF(A66="crop", 0, G66)</f>
         <v>0</v>
       </c>
-      <c r="O66">
+      <c r="M66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S66" s="6" t="s">
+      <c r="Q66" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="T66" s="6">
+      <c r="R66" s="6">
         <v>-0.24</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>101</v>
       </c>
@@ -3505,7 +3513,7 @@
         <v>61</v>
       </c>
       <c r="C67">
-        <f>VLOOKUP(B67, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B67, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D67">
@@ -3516,7 +3524,7 @@
         <v>0</v>
       </c>
       <c r="F67">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G67">
@@ -3531,18 +3539,18 @@
         <f>IF(A67="crop", 0, G67)</f>
         <v>0</v>
       </c>
-      <c r="O67">
+      <c r="M67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S67" s="6" t="s">
+      <c r="Q67" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="T67" s="6">
+      <c r="R67" s="6">
         <v>-0.32</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>101</v>
       </c>
@@ -3550,7 +3558,7 @@
         <v>62</v>
       </c>
       <c r="C68">
-        <f>VLOOKUP(B68, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B68, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.1</v>
       </c>
       <c r="D68">
@@ -3561,7 +3569,7 @@
         <v>-0.72000000000000008</v>
       </c>
       <c r="F68">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G68">
@@ -3576,18 +3584,18 @@
         <f>IF(A68="crop", 0, G68)</f>
         <v>0</v>
       </c>
-      <c r="O68">
+      <c r="M68">
         <f t="shared" si="1"/>
-        <v>-2.5748000000000009E-4</v>
-      </c>
-      <c r="S68" s="6" t="s">
+        <v>-2.5771428571428581E-4</v>
+      </c>
+      <c r="Q68" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="T68" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="R68" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>101</v>
       </c>
@@ -3595,7 +3603,7 @@
         <v>63</v>
       </c>
       <c r="C69">
-        <f>VLOOKUP(B69, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B69, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.33</v>
       </c>
       <c r="D69">
@@ -3606,7 +3614,7 @@
         <v>-2.4090000000000034</v>
       </c>
       <c r="F69">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G69">
@@ -3621,18 +3629,18 @@
         <f>IF(A69="crop", 0, G69)</f>
         <v>0</v>
       </c>
-      <c r="O69">
+      <c r="M69">
         <f t="shared" si="1"/>
-        <v>-8.6148516666666804E-4</v>
-      </c>
-      <c r="S69" s="6" t="s">
+        <v>-8.6226904761904893E-4</v>
+      </c>
+      <c r="Q69" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="T69" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="R69" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>101</v>
       </c>
@@ -3640,7 +3648,7 @@
         <v>64</v>
       </c>
       <c r="C70">
-        <f>VLOOKUP(B70, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B70, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D70">
@@ -3651,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="F70">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G70">
@@ -3666,18 +3674,18 @@
         <f>IF(A70="crop", 0, G70)</f>
         <v>0</v>
       </c>
-      <c r="O70">
+      <c r="M70">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S70" s="6" t="s">
+      <c r="Q70" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="T70" s="6">
+      <c r="R70" s="6">
         <v>-0.1</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>101</v>
       </c>
@@ -3685,7 +3693,7 @@
         <v>65</v>
       </c>
       <c r="C71">
-        <f>VLOOKUP(B71, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B71, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.05</v>
       </c>
       <c r="D71">
@@ -3696,7 +3704,7 @@
         <v>-0.3750000000000005</v>
       </c>
       <c r="F71">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G71">
@@ -3711,18 +3719,18 @@
         <f>IF(A71="crop", 0, G71)</f>
         <v>0</v>
       </c>
-      <c r="O71">
+      <c r="M71">
         <f t="shared" si="1"/>
-        <v>-1.3410416666666687E-4</v>
-      </c>
-      <c r="S71" s="6" t="s">
+        <v>-1.3422619047619066E-4</v>
+      </c>
+      <c r="Q71" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="T71" s="6">
+      <c r="R71" s="6">
         <v>-0.33</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>101</v>
       </c>
@@ -3730,7 +3738,7 @@
         <v>66</v>
       </c>
       <c r="C72">
-        <f>VLOOKUP(B72, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B72, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.26</v>
       </c>
       <c r="D72">
@@ -3741,7 +3749,7 @@
         <v>-1.976</v>
       </c>
       <c r="F72">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G72">
@@ -3756,18 +3764,18 @@
         <f>IF(A72="crop", 0, G72)</f>
         <v>0</v>
       </c>
-      <c r="O72">
+      <c r="M72">
         <f t="shared" si="1"/>
-        <v>-7.0663955555555567E-4</v>
-      </c>
-      <c r="S72" s="6" t="s">
+        <v>-7.0728253968253981E-4</v>
+      </c>
+      <c r="Q72" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="T72" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="R72" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>101</v>
       </c>
@@ -3775,7 +3783,7 @@
         <v>67</v>
       </c>
       <c r="C73">
-        <f>VLOOKUP(B73, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B73, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.26</v>
       </c>
       <c r="D73">
@@ -3786,7 +3794,7 @@
         <v>-2.0020000000000024</v>
       </c>
       <c r="F73">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G73">
@@ -3801,18 +3809,18 @@
         <f>IF(A73="crop", 0, G73)</f>
         <v>0</v>
       </c>
-      <c r="O73">
+      <c r="M73">
         <f t="shared" si="1"/>
-        <v>-7.1593744444444548E-4</v>
-      </c>
-      <c r="S73" s="6" t="s">
+        <v>-7.1658888888888978E-4</v>
+      </c>
+      <c r="Q73" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="T73" s="6">
+      <c r="R73" s="6">
         <v>-0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>101</v>
       </c>
@@ -3820,7 +3828,7 @@
         <v>68</v>
       </c>
       <c r="C74">
-        <f>VLOOKUP(B74, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B74, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.03</v>
       </c>
       <c r="D74">
@@ -3831,7 +3839,7 @@
         <v>-0.23400000000000029</v>
       </c>
       <c r="F74">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G74">
@@ -3846,18 +3854,18 @@
         <f>IF(A74="crop", 0, G74)</f>
         <v>0</v>
       </c>
-      <c r="O74">
+      <c r="M74">
         <f t="shared" si="1"/>
-        <v>-8.3681000000000123E-5</v>
-      </c>
-      <c r="S74" s="6" t="s">
+        <v>-8.3757142857142976E-5</v>
+      </c>
+      <c r="Q74" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="T74" s="6">
+      <c r="R74" s="6">
         <v>-0.26</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>101</v>
       </c>
@@ -3865,7 +3873,7 @@
         <v>69</v>
       </c>
       <c r="C75">
-        <f>VLOOKUP(B75, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B75, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.37</v>
       </c>
       <c r="D75">
@@ -3876,7 +3884,7 @@
         <v>-2.9230000000000036</v>
       </c>
       <c r="F75">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G75">
@@ -3891,18 +3899,18 @@
         <f>IF(A75="crop", 0, G75)</f>
         <v>0</v>
       </c>
-      <c r="O75">
+      <c r="M75">
         <f t="shared" si="1"/>
-        <v>-1.045297277777779E-3</v>
-      </c>
-      <c r="S75" s="6" t="s">
+        <v>-1.0462484126984139E-3</v>
+      </c>
+      <c r="Q75" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="T75" s="6">
+      <c r="R75" s="6">
         <v>-0.26</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>101</v>
       </c>
@@ -3910,7 +3918,7 @@
         <v>70</v>
       </c>
       <c r="C76">
-        <f>VLOOKUP(B76, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B76, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.01</v>
       </c>
       <c r="D76">
@@ -3921,7 +3929,7 @@
         <v>-8.0000000000000113E-2</v>
       </c>
       <c r="F76">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G76">
@@ -3936,18 +3944,18 @@
         <f>IF(A76="crop", 0, G76)</f>
         <v>0</v>
       </c>
-      <c r="O76">
-        <f t="shared" ref="O76:O83" si="3">(H76*$L$11+I76*$M$11)*$N$11</f>
-        <v>-2.8608888888888932E-5</v>
-      </c>
-      <c r="S76" s="6" t="s">
+      <c r="M76">
+        <f t="shared" ref="M76:M83" si="3">(H76*$J$11+I76*$K$11)*$L$11</f>
+        <v>-2.8634920634920675E-5</v>
+      </c>
+      <c r="Q76" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="T76" s="6">
+      <c r="R76" s="6">
         <v>-0.03</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>101</v>
       </c>
@@ -3955,7 +3963,7 @@
         <v>71</v>
       </c>
       <c r="C77">
-        <f>VLOOKUP(B77, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B77, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.03</v>
       </c>
       <c r="D77">
@@ -3966,7 +3974,7 @@
         <v>-0.2430000000000003</v>
       </c>
       <c r="F77">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G77">
@@ -3981,18 +3989,18 @@
         <f>IF(A77="crop", 0, G77)</f>
         <v>0</v>
       </c>
-      <c r="O77">
+      <c r="M77">
         <f t="shared" si="3"/>
-        <v>-8.6899500000000126E-5</v>
-      </c>
-      <c r="S77" s="6" t="s">
+        <v>-8.6978571428571554E-5</v>
+      </c>
+      <c r="Q77" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="T77" s="6">
+      <c r="R77" s="6">
         <v>-0.37</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>101</v>
       </c>
@@ -4000,7 +4008,7 @@
         <v>72</v>
       </c>
       <c r="C78">
-        <f>VLOOKUP(B78, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B78, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.1</v>
       </c>
       <c r="D78">
@@ -4011,7 +4019,7 @@
         <v>-0.82000000000000106</v>
       </c>
       <c r="F78">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G78">
@@ -4026,18 +4034,18 @@
         <f>IF(A78="crop", 0, G78)</f>
         <v>0</v>
       </c>
-      <c r="O78">
+      <c r="M78">
         <f t="shared" si="3"/>
-        <v>-2.9324111111111154E-4</v>
-      </c>
-      <c r="S78" s="6" t="s">
+        <v>-2.9350793650793688E-4</v>
+      </c>
+      <c r="Q78" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="T78" s="6">
+      <c r="R78" s="6">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>101</v>
       </c>
@@ -4045,7 +4053,7 @@
         <v>73</v>
       </c>
       <c r="C79">
-        <f>VLOOKUP(B79, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B79, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.25</v>
       </c>
       <c r="D79">
@@ -4056,7 +4064,7 @@
         <v>-2.0750000000000024</v>
       </c>
       <c r="F79">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G79">
@@ -4071,18 +4079,18 @@
         <f>IF(A79="crop", 0, G79)</f>
         <v>0</v>
       </c>
-      <c r="O79">
+      <c r="M79">
         <f t="shared" si="3"/>
-        <v>-7.4204305555555653E-4</v>
-      </c>
-      <c r="S79" s="6" t="s">
+        <v>-7.4271825396825491E-4</v>
+      </c>
+      <c r="Q79" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="T79" s="6">
+      <c r="R79" s="6">
         <v>-0.03</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>101</v>
       </c>
@@ -4090,7 +4098,7 @@
         <v>74</v>
       </c>
       <c r="C80">
-        <f>VLOOKUP(B80, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B80, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.27</v>
       </c>
       <c r="D80">
@@ -4101,7 +4109,7 @@
         <v>-2.2680000000000025</v>
       </c>
       <c r="F80">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G80">
@@ -4116,18 +4124,18 @@
         <f>IF(A80="crop", 0, G80)</f>
         <v>0</v>
       </c>
-      <c r="O80">
+      <c r="M80">
         <f t="shared" si="3"/>
-        <v>-8.1106200000000107E-4</v>
-      </c>
-      <c r="S80" s="6" t="s">
+        <v>-8.1180000000000098E-4</v>
+      </c>
+      <c r="Q80" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="T80" s="6">
+      <c r="R80" s="6">
         <v>-0.1</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>101</v>
       </c>
@@ -4135,7 +4143,7 @@
         <v>75</v>
       </c>
       <c r="C81">
-        <f>VLOOKUP(B81, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B81, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.18</v>
       </c>
       <c r="D81">
@@ -4146,7 +4154,7 @@
         <v>-1.5300000000000018</v>
       </c>
       <c r="F81">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G81">
@@ -4161,18 +4169,18 @@
         <f>IF(A81="crop", 0, G81)</f>
         <v>0</v>
       </c>
-      <c r="O81">
+      <c r="M81">
         <f t="shared" si="3"/>
-        <v>-5.4714500000000073E-4</v>
-      </c>
-      <c r="S81" s="6" t="s">
+        <v>-5.4764285714285787E-4</v>
+      </c>
+      <c r="Q81" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="T81" s="6">
+      <c r="R81" s="6">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>101</v>
       </c>
@@ -4180,7 +4188,7 @@
         <v>76</v>
       </c>
       <c r="C82">
-        <f>VLOOKUP(B82, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B82, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.12</v>
       </c>
       <c r="D82">
@@ -4191,7 +4199,7 @@
         <v>-1.0320000000000011</v>
       </c>
       <c r="F82">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G82">
@@ -4206,18 +4214,18 @@
         <f>IF(A82="crop", 0, G82)</f>
         <v>0</v>
       </c>
-      <c r="O82">
+      <c r="M82">
         <f t="shared" si="3"/>
-        <v>-3.6905466666666714E-4</v>
-      </c>
-      <c r="S82" s="6" t="s">
+        <v>-3.6939047619047663E-4</v>
+      </c>
+      <c r="Q82" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="T82" s="6">
+      <c r="R82" s="6">
         <v>-0.27</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>101</v>
       </c>
@@ -4225,7 +4233,7 @@
         <v>77</v>
       </c>
       <c r="C83">
-        <f>VLOOKUP(B83, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B83, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.22</v>
       </c>
       <c r="D83">
@@ -4236,7 +4244,7 @@
         <v>-1.9140000000000021</v>
       </c>
       <c r="F83">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G83">
@@ -4251,18 +4259,18 @@
         <f>IF(A83="crop", 0, G83)</f>
         <v>0</v>
       </c>
-      <c r="O83">
+      <c r="M83">
         <f t="shared" si="3"/>
-        <v>-6.8446766666666753E-4</v>
-      </c>
-      <c r="S83" s="6" t="s">
+        <v>-6.8509047619047699E-4</v>
+      </c>
+      <c r="Q83" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="T83" s="6">
+      <c r="R83" s="6">
         <v>-0.18</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>101</v>
       </c>
@@ -4270,7 +4278,7 @@
         <v>78</v>
       </c>
       <c r="C84">
-        <f>VLOOKUP(B84, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B84, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.2</v>
       </c>
       <c r="D84">
@@ -4281,7 +4289,7 @@
         <v>-1.760000000000002</v>
       </c>
       <c r="F84">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G84">
@@ -4296,18 +4304,18 @@
         <f>IF(A84="crop", 0, G84)</f>
         <v>0</v>
       </c>
-      <c r="O84">
-        <f>(H84*$L$11+I84*$M$11)*$N$11</f>
-        <v>-6.2939555555555635E-4</v>
-      </c>
-      <c r="S84" s="6" t="s">
+      <c r="M84">
+        <f>(H84*$J$11+I84*$K$11)*$L$11</f>
+        <v>-6.2996825396825469E-4</v>
+      </c>
+      <c r="Q84" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="T84" s="6">
+      <c r="R84" s="6">
         <v>-0.12</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>101</v>
       </c>
@@ -4315,7 +4323,7 @@
         <v>79</v>
       </c>
       <c r="C85">
-        <f>VLOOKUP(B85, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B85, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.18</v>
       </c>
       <c r="D85">
@@ -4326,7 +4334,7 @@
         <v>-1.6020000000000016</v>
       </c>
       <c r="F85">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G85">
@@ -4341,18 +4349,18 @@
         <f>IF(A85="crop", 0, G85)</f>
         <v>0</v>
       </c>
-      <c r="O85">
-        <f t="shared" ref="O85:O128" si="4">(H85*$L$11+I85*$M$11)*$N$11</f>
-        <v>-5.7289300000000064E-4</v>
-      </c>
-      <c r="S85" s="6" t="s">
+      <c r="M85">
+        <f t="shared" ref="M85:M128" si="4">(H85*$J$11+I85*$K$11)*$L$11</f>
+        <v>-5.7341428571428639E-4</v>
+      </c>
+      <c r="Q85" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="T85" s="6">
+      <c r="R85" s="6">
         <v>-0.22</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>101</v>
       </c>
@@ -4360,7 +4368,7 @@
         <v>80</v>
       </c>
       <c r="C86">
-        <f>VLOOKUP(B86, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B86, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.4</v>
       </c>
       <c r="D86">
@@ -4371,7 +4379,7 @@
         <v>-3.6000000000000045</v>
       </c>
       <c r="F86">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G86">
@@ -4386,18 +4394,18 @@
         <f>IF(A86="crop", 0, G86)</f>
         <v>0</v>
       </c>
-      <c r="O86">
+      <c r="M86">
         <f t="shared" si="4"/>
-        <v>-1.2874000000000019E-3</v>
-      </c>
-      <c r="S86" s="6" t="s">
+        <v>-1.2885714285714304E-3</v>
+      </c>
+      <c r="Q86" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="T86" s="6">
+      <c r="R86" s="6">
         <v>-0.2</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>101</v>
       </c>
@@ -4405,7 +4413,7 @@
         <v>81</v>
       </c>
       <c r="C87">
-        <f>VLOOKUP(B87, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B87, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.21</v>
       </c>
       <c r="D87">
@@ -4416,7 +4424,7 @@
         <v>-1.911000000000002</v>
       </c>
       <c r="F87">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G87">
@@ -4431,18 +4439,18 @@
         <f>IF(A87="crop", 0, G87)</f>
         <v>0</v>
       </c>
-      <c r="O87">
+      <c r="M87">
         <f t="shared" si="4"/>
-        <v>-6.8339483333333423E-4</v>
-      </c>
-      <c r="S87" s="6" t="s">
+        <v>-6.8401666666666747E-4</v>
+      </c>
+      <c r="Q87" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="T87" s="6">
+      <c r="R87" s="6">
         <v>-0.18</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>101</v>
       </c>
@@ -4450,7 +4458,7 @@
         <v>82</v>
       </c>
       <c r="C88">
-        <f>VLOOKUP(B88, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B88, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.39</v>
       </c>
       <c r="D88">
@@ -4461,7 +4469,7 @@
         <v>-3.5880000000000041</v>
       </c>
       <c r="F88">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G88">
@@ -4476,18 +4484,18 @@
         <f>IF(A88="crop", 0, G88)</f>
         <v>0</v>
       </c>
-      <c r="O88">
+      <c r="M88">
         <f t="shared" si="4"/>
-        <v>-1.2831086666666683E-3</v>
-      </c>
-      <c r="S88" s="6" t="s">
+        <v>-1.2842761904761921E-3</v>
+      </c>
+      <c r="Q88" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="T88" s="6">
+      <c r="R88" s="6">
         <v>-0.4</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>101</v>
       </c>
@@ -4495,7 +4503,7 @@
         <v>83</v>
       </c>
       <c r="C89">
-        <f>VLOOKUP(B89, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B89, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.69</v>
       </c>
       <c r="D89">
@@ -4506,7 +4514,7 @@
         <v>-6.417000000000006</v>
       </c>
       <c r="F89">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G89">
@@ -4521,18 +4529,18 @@
         <f>IF(A89="crop", 0, G89)</f>
         <v>0</v>
       </c>
-      <c r="O89">
+      <c r="M89">
         <f t="shared" si="4"/>
-        <v>-2.2947905000000024E-3</v>
-      </c>
-      <c r="S89" s="6" t="s">
+        <v>-2.2968785714285738E-3</v>
+      </c>
+      <c r="Q89" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="T89" s="6">
+      <c r="R89" s="6">
         <v>-0.21</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>101</v>
       </c>
@@ -4540,7 +4548,7 @@
         <v>84</v>
       </c>
       <c r="C90">
-        <f>VLOOKUP(B90, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B90, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D90">
@@ -4551,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="F90">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G90">
@@ -4566,18 +4574,18 @@
         <f>IF(A90="crop", 0, G90)</f>
         <v>0</v>
       </c>
-      <c r="O90">
+      <c r="M90">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S90" s="6" t="s">
+      <c r="Q90" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="T90" s="6">
+      <c r="R90" s="6">
         <v>-0.39</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>101</v>
       </c>
@@ -4585,7 +4593,7 @@
         <v>85</v>
       </c>
       <c r="C91">
-        <f>VLOOKUP(B91, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B91, $Q$13:$R$96, 2, FALSE)</f>
         <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D91">
@@ -4596,7 +4604,7 @@
         <v>-0.66500000000000081</v>
       </c>
       <c r="F91">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G91">
@@ -4611,18 +4619,18 @@
         <f>IF(A91="crop", 0, G91)</f>
         <v>0</v>
       </c>
-      <c r="O91">
+      <c r="M91">
         <f t="shared" si="4"/>
-        <v>-2.3781138888888918E-4</v>
-      </c>
-      <c r="S91" s="6" t="s">
+        <v>-2.3802777777777806E-4</v>
+      </c>
+      <c r="Q91" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="T91" s="6">
+      <c r="R91" s="6">
         <v>-0.69</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>101</v>
       </c>
@@ -4630,7 +4638,7 @@
         <v>86</v>
       </c>
       <c r="C92">
-        <f>VLOOKUP(B92, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B92, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.56999999999999995</v>
       </c>
       <c r="D92">
@@ -4641,7 +4649,7 @@
         <v>-5.4720000000000057</v>
       </c>
       <c r="F92">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G92">
@@ -4656,18 +4664,18 @@
         <f>IF(A92="crop", 0, G92)</f>
         <v>0</v>
       </c>
-      <c r="O92">
+      <c r="M92">
         <f t="shared" si="4"/>
-        <v>-1.9568480000000023E-3</v>
-      </c>
-      <c r="S92" s="6" t="s">
+        <v>-1.9586285714285737E-3</v>
+      </c>
+      <c r="Q92" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="T92" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="R92" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>101</v>
       </c>
@@ -4675,7 +4683,7 @@
         <v>87</v>
       </c>
       <c r="C93">
-        <f>VLOOKUP(B93, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B93, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.67</v>
       </c>
       <c r="D93">
@@ -4686,7 +4694,7 @@
         <v>-6.4990000000000068</v>
       </c>
       <c r="F93">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G93">
@@ -4701,18 +4709,18 @@
         <f>IF(A93="crop", 0, G93)</f>
         <v>0</v>
       </c>
-      <c r="O93">
+      <c r="M93">
         <f t="shared" si="4"/>
-        <v>-2.3241146111111135E-3</v>
-      </c>
-      <c r="S93" s="6" t="s">
+        <v>-2.3262293650793673E-3</v>
+      </c>
+      <c r="Q93" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="T93" s="6">
+      <c r="R93" s="6">
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>101</v>
       </c>
@@ -4720,7 +4728,7 @@
         <v>88</v>
       </c>
       <c r="C94">
-        <f>VLOOKUP(B94, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B94, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.05</v>
       </c>
       <c r="D94">
@@ -4731,7 +4739,7 @@
         <v>-0.49000000000000049</v>
       </c>
       <c r="F94">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G94">
@@ -4746,18 +4754,18 @@
         <f>IF(A94="crop", 0, G94)</f>
         <v>0</v>
       </c>
-      <c r="O94">
+      <c r="M94">
         <f t="shared" si="4"/>
-        <v>-1.7522944444444463E-4</v>
-      </c>
-      <c r="S94" s="6" t="s">
+        <v>-1.7538888888888907E-4</v>
+      </c>
+      <c r="Q94" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="T94" s="6">
+      <c r="R94" s="6">
         <v>-0.56999999999999995</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>102</v>
       </c>
@@ -4765,7 +4773,7 @@
         <v>5</v>
       </c>
       <c r="C95">
-        <f>VLOOKUP(B95, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B95, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.12</v>
       </c>
       <c r="D95">
@@ -4776,7 +4784,7 @@
         <v>-1.296</v>
       </c>
       <c r="F95">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G95">
@@ -4791,18 +4799,18 @@
         <f>IF(A95="crop", 0, G95)</f>
         <v>-7.2000000000000008E-2</v>
       </c>
-      <c r="O95">
+      <c r="M95">
         <f t="shared" si="4"/>
-        <v>-2.0347200000000001E-4</v>
-      </c>
-      <c r="S95" s="6" t="s">
+        <v>-2.0365714285714285E-4</v>
+      </c>
+      <c r="Q95" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="T95" s="6">
+      <c r="R95" s="6">
         <v>-0.67</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>102</v>
       </c>
@@ -4810,7 +4818,7 @@
         <v>6</v>
       </c>
       <c r="C96">
-        <f>VLOOKUP(B96, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B96, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.39</v>
       </c>
       <c r="D96">
@@ -4821,7 +4829,7 @@
         <v>-4.6020000000000003</v>
       </c>
       <c r="F96">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G96">
@@ -4836,18 +4844,18 @@
         <f>IF(A96="crop", 0, G96)</f>
         <v>-0.25566666666666671</v>
       </c>
-      <c r="O96">
+      <c r="M96">
         <f t="shared" si="4"/>
-        <v>-7.2251400000000016E-4</v>
-      </c>
-      <c r="S96" s="6" t="s">
+        <v>-7.2317142857142866E-4</v>
+      </c>
+      <c r="Q96" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="T96" s="6">
+      <c r="R96" s="6">
         <v>-0.05</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>102</v>
       </c>
@@ -4855,7 +4863,7 @@
         <v>7</v>
       </c>
       <c r="C97">
-        <f>VLOOKUP(B97, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B97, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.09</v>
       </c>
       <c r="D97">
@@ -4866,7 +4874,7 @@
         <v>-1.1519999999999999</v>
       </c>
       <c r="F97">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G97">
@@ -4881,12 +4889,12 @@
         <f>IF(A97="crop", 0, G97)</f>
         <v>-6.4000000000000001E-2</v>
       </c>
-      <c r="O97">
+      <c r="M97">
         <f t="shared" si="4"/>
-        <v>-1.8086400000000001E-4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.8102857142857141E-4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>102</v>
       </c>
@@ -4894,7 +4902,7 @@
         <v>8</v>
       </c>
       <c r="C98">
-        <f>VLOOKUP(B98, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B98, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.09</v>
       </c>
       <c r="D98">
@@ -4905,7 +4913,7 @@
         <v>-1.242</v>
       </c>
       <c r="F98">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G98">
@@ -4920,12 +4928,12 @@
         <f>IF(A98="crop", 0, G98)</f>
         <v>-6.9000000000000006E-2</v>
       </c>
-      <c r="O98">
+      <c r="M98">
         <f t="shared" si="4"/>
-        <v>-1.9499400000000001E-4</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.951714285714286E-4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>102</v>
       </c>
@@ -4933,7 +4941,7 @@
         <v>9</v>
       </c>
       <c r="C99">
-        <f>VLOOKUP(B99, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B99, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.13</v>
       </c>
       <c r="D99">
@@ -4944,7 +4952,7 @@
         <v>-1.9240000000000002</v>
       </c>
       <c r="F99">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G99">
@@ -4959,12 +4967,12 @@
         <f>IF(A99="crop", 0, G99)</f>
         <v>-0.10688888888888889</v>
       </c>
-      <c r="O99">
+      <c r="M99">
         <f t="shared" si="4"/>
-        <v>-3.0206800000000001E-4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-3.0234285714285717E-4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>102</v>
       </c>
@@ -4972,7 +4980,7 @@
         <v>10</v>
       </c>
       <c r="C100">
-        <f>VLOOKUP(B100, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B100, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.13</v>
       </c>
       <c r="D100">
@@ -4983,7 +4991,7 @@
         <v>-2.0540000000000003</v>
       </c>
       <c r="F100">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G100">
@@ -4998,12 +5006,12 @@
         <f>IF(A100="crop", 0, G100)</f>
         <v>-0.11411111111111112</v>
       </c>
-      <c r="O100">
+      <c r="M100">
         <f t="shared" si="4"/>
-        <v>-3.2247800000000001E-4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-3.2277142857142858E-4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>102</v>
       </c>
@@ -5011,7 +5019,7 @@
         <v>11</v>
       </c>
       <c r="C101">
-        <f>VLOOKUP(B101, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B101, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.55000000000000004</v>
       </c>
       <c r="D101">
@@ -5022,7 +5030,7 @@
         <v>-9.240000000000002</v>
       </c>
       <c r="F101">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G101">
@@ -5037,12 +5045,12 @@
         <f>IF(A101="crop", 0, G101)</f>
         <v>-0.51333333333333342</v>
       </c>
-      <c r="O101">
+      <c r="M101">
         <f t="shared" si="4"/>
-        <v>-1.4506800000000002E-3</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.4520000000000002E-3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>102</v>
       </c>
@@ -5050,7 +5058,7 @@
         <v>12</v>
       </c>
       <c r="C102">
-        <f>VLOOKUP(B102, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B102, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.01</v>
       </c>
       <c r="D102">
@@ -5061,7 +5069,7 @@
         <v>-0.17800000000000002</v>
       </c>
       <c r="F102">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G102">
@@ -5076,12 +5084,12 @@
         <f>IF(A102="crop", 0, G102)</f>
         <v>-9.8888888888888898E-3</v>
       </c>
-      <c r="O102">
+      <c r="M102">
         <f t="shared" si="4"/>
-        <v>-2.7946000000000003E-5</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-2.7971428571428573E-5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -5089,7 +5097,7 @@
         <v>13</v>
       </c>
       <c r="C103">
-        <f>VLOOKUP(B103, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B103, $Q$13:$R$96, 2, FALSE)</f>
         <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D103">
@@ -5100,7 +5108,7 @@
         <v>-1.3160000000000003</v>
       </c>
       <c r="F103">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G103">
@@ -5115,12 +5123,12 @@
         <f>IF(A103="crop", 0, G103)</f>
         <v>-7.3111111111111127E-2</v>
       </c>
-      <c r="O103">
+      <c r="M103">
         <f t="shared" si="4"/>
-        <v>-2.0661200000000006E-4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-2.0680000000000004E-4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>102</v>
       </c>
@@ -5128,7 +5136,7 @@
         <v>14</v>
       </c>
       <c r="C104">
-        <f>VLOOKUP(B104, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B104, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.06</v>
       </c>
       <c r="D104">
@@ -5139,7 +5147,7 @@
         <v>-1.1879999999999999</v>
       </c>
       <c r="F104">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G104">
@@ -5154,12 +5162,12 @@
         <f>IF(A104="crop", 0, G104)</f>
         <v>-6.6000000000000003E-2</v>
       </c>
-      <c r="O104">
+      <c r="M104">
         <f t="shared" si="4"/>
-        <v>-1.8651600000000001E-4</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.8668571428571428E-4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>102</v>
       </c>
@@ -5167,7 +5175,7 @@
         <v>15</v>
       </c>
       <c r="C105">
-        <f>VLOOKUP(B105, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B105, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.09</v>
       </c>
       <c r="D105">
@@ -5178,7 +5186,7 @@
         <v>-1.8719999999999999</v>
       </c>
       <c r="F105">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G105">
@@ -5193,12 +5201,12 @@
         <f>IF(A105="crop", 0, G105)</f>
         <v>-0.104</v>
       </c>
-      <c r="O105">
+      <c r="M105">
         <f t="shared" si="4"/>
-        <v>-2.93904E-4</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-2.9417142857142854E-4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>102</v>
       </c>
@@ -5206,7 +5214,7 @@
         <v>16</v>
       </c>
       <c r="C106">
-        <f>VLOOKUP(B106, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B106, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.19</v>
       </c>
       <c r="D106">
@@ -5217,7 +5225,7 @@
         <v>-4.1420000000000003</v>
       </c>
       <c r="F106">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G106">
@@ -5232,12 +5240,12 @@
         <f>IF(A106="crop", 0, G106)</f>
         <v>-0.23011111111111113</v>
       </c>
-      <c r="O106">
+      <c r="M106">
         <f t="shared" si="4"/>
-        <v>-6.5029400000000005E-4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-6.5088571428571437E-4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>102</v>
       </c>
@@ -5245,7 +5253,7 @@
         <v>17</v>
       </c>
       <c r="C107">
-        <f>VLOOKUP(B107, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B107, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.13</v>
       </c>
       <c r="D107">
@@ -5256,7 +5264,7 @@
         <v>-2.9640000000000004</v>
       </c>
       <c r="F107">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G107">
@@ -5271,12 +5279,12 @@
         <f>IF(A107="crop", 0, G107)</f>
         <v>-0.16466666666666668</v>
       </c>
-      <c r="O107">
+      <c r="M107">
         <f t="shared" si="4"/>
-        <v>-4.6534800000000009E-4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-4.6577142857142864E-4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>102</v>
       </c>
@@ -5284,7 +5292,7 @@
         <v>18</v>
       </c>
       <c r="C108">
-        <f>VLOOKUP(B108, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B108, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.04</v>
       </c>
       <c r="D108">
@@ -5295,7 +5303,7 @@
         <v>-0.95200000000000007</v>
       </c>
       <c r="F108">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G108">
@@ -5310,12 +5318,12 @@
         <f>IF(A108="crop", 0, G108)</f>
         <v>-5.2888888888888895E-2</v>
       </c>
-      <c r="O108">
+      <c r="M108">
         <f t="shared" si="4"/>
-        <v>-1.4946400000000003E-4</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.496E-4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>102</v>
       </c>
@@ -5323,7 +5331,7 @@
         <v>19</v>
       </c>
       <c r="C109">
-        <f>VLOOKUP(B109, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B109, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.4</v>
       </c>
       <c r="D109">
@@ -5334,7 +5342,7 @@
         <v>-9.9200000000000017</v>
       </c>
       <c r="F109">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G109">
@@ -5349,12 +5357,12 @@
         <f>IF(A109="crop", 0, G109)</f>
         <v>-0.55111111111111122</v>
       </c>
-      <c r="O109">
+      <c r="M109">
         <f t="shared" si="4"/>
-        <v>-1.5574400000000004E-3</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.5588571428571433E-3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>102</v>
       </c>
@@ -5362,7 +5370,7 @@
         <v>20</v>
       </c>
       <c r="C110">
-        <f>VLOOKUP(B110, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B110, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.09</v>
       </c>
       <c r="D110">
@@ -5373,7 +5381,7 @@
         <v>-2.3220000000000001</v>
       </c>
       <c r="F110">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G110">
@@ -5388,12 +5396,12 @@
         <f>IF(A110="crop", 0, G110)</f>
         <v>-0.129</v>
       </c>
-      <c r="O110">
+      <c r="M110">
         <f t="shared" si="4"/>
-        <v>-3.6455400000000001E-4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-3.648857142857143E-4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>102</v>
       </c>
@@ -5401,7 +5409,7 @@
         <v>21</v>
       </c>
       <c r="C111">
-        <f>VLOOKUP(B111, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B111, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D111">
@@ -5412,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="F111">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G111">
@@ -5427,12 +5435,12 @@
         <f>IF(A111="crop", 0, G111)</f>
         <v>0</v>
       </c>
-      <c r="O111">
+      <c r="M111">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>102</v>
       </c>
@@ -5440,7 +5448,7 @@
         <v>22</v>
       </c>
       <c r="C112">
-        <f>VLOOKUP(B112, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B112, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.44</v>
       </c>
       <c r="D112">
@@ -5451,7 +5459,7 @@
         <v>-12.232000000000001</v>
       </c>
       <c r="F112">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G112">
@@ -5466,12 +5474,12 @@
         <f>IF(A112="crop", 0, G112)</f>
         <v>-0.67955555555555558</v>
       </c>
-      <c r="O112">
+      <c r="M112">
         <f t="shared" si="4"/>
-        <v>-1.9204240000000002E-3</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.9221714285714286E-3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>102</v>
       </c>
@@ -5479,7 +5487,7 @@
         <v>23</v>
       </c>
       <c r="C113">
-        <f>VLOOKUP(B113, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B113, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.21</v>
       </c>
       <c r="D113">
@@ -5490,7 +5498,7 @@
         <v>-6.048</v>
       </c>
       <c r="F113">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G113">
@@ -5505,12 +5513,12 @@
         <f>IF(A113="crop", 0, G113)</f>
         <v>-0.33600000000000002</v>
       </c>
-      <c r="O113">
+      <c r="M113">
         <f t="shared" si="4"/>
-        <v>-9.4953600000000017E-4</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-9.5040000000000012E-4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>102</v>
       </c>
@@ -5518,7 +5526,7 @@
         <v>24</v>
       </c>
       <c r="C114">
-        <f>VLOOKUP(B114, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B114, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.21</v>
       </c>
       <c r="D114">
@@ -5529,7 +5537,7 @@
         <v>-6.258</v>
       </c>
       <c r="F114">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G114">
@@ -5544,12 +5552,12 @@
         <f>IF(A114="crop", 0, G114)</f>
         <v>-0.34766666666666668</v>
       </c>
-      <c r="O114">
+      <c r="M114">
         <f t="shared" si="4"/>
-        <v>-9.8250600000000018E-4</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-9.8339999999999994E-4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>102</v>
       </c>
@@ -5557,7 +5565,7 @@
         <v>25</v>
       </c>
       <c r="C115">
-        <f>VLOOKUP(B115, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B115, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D115">
@@ -5568,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="F115">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G115">
@@ -5583,12 +5591,12 @@
         <f>IF(A115="crop", 0, G115)</f>
         <v>0</v>
       </c>
-      <c r="O115">
+      <c r="M115">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>102</v>
       </c>
@@ -5596,7 +5604,7 @@
         <v>26</v>
       </c>
       <c r="C116">
-        <f>VLOOKUP(B116, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B116, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.04</v>
       </c>
       <c r="D116">
@@ -5607,7 +5615,7 @@
         <v>-1.272</v>
       </c>
       <c r="F116">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G116">
@@ -5622,12 +5630,12 @@
         <f>IF(A116="crop", 0, G116)</f>
         <v>-7.0666666666666669E-2</v>
       </c>
-      <c r="O116">
+      <c r="M116">
         <f t="shared" si="4"/>
-        <v>-1.9970400000000001E-4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.9988571428571428E-4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>102</v>
       </c>
@@ -5635,7 +5643,7 @@
         <v>27</v>
       </c>
       <c r="C117">
-        <f>VLOOKUP(B117, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B117, $Q$13:$R$96, 2, FALSE)</f>
         <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D117">
@@ -5646,7 +5654,7 @@
         <v>-2.2959999999999998</v>
       </c>
       <c r="F117">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G117">
@@ -5661,12 +5669,12 @@
         <f>IF(A117="crop", 0, G117)</f>
         <v>-0.12755555555555553</v>
       </c>
-      <c r="O117">
+      <c r="M117">
         <f t="shared" si="4"/>
-        <v>-3.6047199999999992E-4</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-3.6079999999999988E-4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>102</v>
       </c>
@@ -5674,7 +5682,7 @@
         <v>28</v>
       </c>
       <c r="C118">
-        <f>VLOOKUP(B118, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B118, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.04</v>
       </c>
       <c r="D118">
@@ -5685,7 +5693,7 @@
         <v>-1.3519999999999999</v>
       </c>
       <c r="F118">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G118">
@@ -5700,12 +5708,12 @@
         <f>IF(A118="crop", 0, G118)</f>
         <v>-7.5111111111111101E-2</v>
       </c>
-      <c r="O118">
+      <c r="M118">
         <f t="shared" si="4"/>
-        <v>-2.1226399999999999E-4</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-2.1245714285714282E-4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>102</v>
       </c>
@@ -5713,7 +5721,7 @@
         <v>29</v>
       </c>
       <c r="C119">
-        <f>VLOOKUP(B119, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B119, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.24</v>
       </c>
       <c r="D119">
@@ -5724,7 +5732,7 @@
         <v>-8.3519999999999985</v>
       </c>
       <c r="F119">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G119">
@@ -5739,12 +5747,12 @@
         <f>IF(A119="crop", 0, G119)</f>
         <v>-0.46399999999999991</v>
       </c>
-      <c r="O119">
+      <c r="M119">
         <f t="shared" si="4"/>
-        <v>-1.3112639999999997E-3</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.3124571428571425E-3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>102</v>
       </c>
@@ -5752,7 +5760,7 @@
         <v>30</v>
       </c>
       <c r="C120">
-        <f>VLOOKUP(B120, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B120, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.17</v>
       </c>
       <c r="D120">
@@ -5763,7 +5771,7 @@
         <v>-6.0860000000000003</v>
       </c>
       <c r="F120">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G120">
@@ -5778,12 +5786,12 @@
         <f>IF(A120="crop", 0, G120)</f>
         <v>-0.33811111111111114</v>
       </c>
-      <c r="O120">
+      <c r="M120">
         <f t="shared" si="4"/>
-        <v>-9.5550200000000011E-4</v>
-      </c>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-9.5637142857142858E-4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>102</v>
       </c>
@@ -5791,7 +5799,7 @@
         <v>31</v>
       </c>
       <c r="C121">
-        <f>VLOOKUP(B121, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B121, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.03</v>
       </c>
       <c r="D121">
@@ -5802,7 +5810,7 @@
         <v>-1.1039999999999999</v>
       </c>
       <c r="F121">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G121">
@@ -5817,12 +5825,12 @@
         <f>IF(A121="crop", 0, G121)</f>
         <v>-6.1333333333333323E-2</v>
       </c>
-      <c r="O121">
+      <c r="M121">
         <f t="shared" si="4"/>
-        <v>-1.7332799999999996E-4</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.7348571428571423E-4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>102</v>
       </c>
@@ -5830,7 +5838,7 @@
         <v>32</v>
       </c>
       <c r="C122">
-        <f>VLOOKUP(B122, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B122, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.02</v>
       </c>
       <c r="D122">
@@ -5841,7 +5849,7 @@
         <v>-0.75600000000000001</v>
       </c>
       <c r="F122">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G122">
@@ -5856,12 +5864,12 @@
         <f>IF(A122="crop", 0, G122)</f>
         <v>-4.2000000000000003E-2</v>
       </c>
-      <c r="O122">
+      <c r="M122">
         <f t="shared" si="4"/>
-        <v>-1.1869200000000002E-4</v>
-      </c>
-    </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.1880000000000001E-4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>102</v>
       </c>
@@ -5869,7 +5877,7 @@
         <v>33</v>
       </c>
       <c r="C123">
-        <f>VLOOKUP(B123, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B123, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.43</v>
       </c>
       <c r="D123">
@@ -5880,7 +5888,7 @@
         <v>-16.683999999999997</v>
       </c>
       <c r="F123">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G123">
@@ -5895,12 +5903,12 @@
         <f>IF(A123="crop", 0, G123)</f>
         <v>-0.92688888888888876</v>
       </c>
-      <c r="O123">
+      <c r="M123">
         <f t="shared" si="4"/>
-        <v>-2.6193879999999998E-3</v>
-      </c>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-2.6217714285714281E-3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>102</v>
       </c>
@@ -5908,7 +5916,7 @@
         <v>34</v>
       </c>
       <c r="C124">
-        <f>VLOOKUP(B124, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B124, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.14000000000000001</v>
       </c>
       <c r="D124">
@@ -5919,7 +5927,7 @@
         <v>-5.5720000000000001</v>
       </c>
       <c r="F124">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G124">
@@ -5934,12 +5942,12 @@
         <f>IF(A124="crop", 0, G124)</f>
         <v>-0.30955555555555558</v>
       </c>
-      <c r="O124">
+      <c r="M124">
         <f t="shared" si="4"/>
-        <v>-8.7480399999999997E-4</v>
-      </c>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-8.7559999999999992E-4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>102</v>
       </c>
@@ -5947,7 +5955,7 @@
         <v>35</v>
       </c>
       <c r="C125">
-        <f>VLOOKUP(B125, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B125, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D125">
@@ -5958,7 +5966,7 @@
         <v>0</v>
       </c>
       <c r="F125">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G125">
@@ -5973,12 +5981,12 @@
         <f>IF(A125="crop", 0, G125)</f>
         <v>0</v>
       </c>
-      <c r="O125">
+      <c r="M125">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>102</v>
       </c>
@@ -5986,7 +5994,7 @@
         <v>36</v>
       </c>
       <c r="C126">
-        <f>VLOOKUP(B126, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B126, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.12</v>
       </c>
       <c r="D126">
@@ -5997,7 +6005,7 @@
         <v>-5.0159999999999991</v>
       </c>
       <c r="F126">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G126">
@@ -6012,12 +6020,12 @@
         <f>IF(A126="crop", 0, G126)</f>
         <v>-0.27866666666666662</v>
       </c>
-      <c r="O126">
+      <c r="M126">
         <f t="shared" si="4"/>
-        <v>-7.8751199999999998E-4</v>
-      </c>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-7.8822857142857132E-4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>102</v>
       </c>
@@ -6025,7 +6033,7 @@
         <v>37</v>
       </c>
       <c r="C127">
-        <f>VLOOKUP(B127, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B127, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.13</v>
       </c>
       <c r="D127">
@@ -6036,7 +6044,7 @@
         <v>-5.5640000000000001</v>
       </c>
       <c r="F127">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G127">
@@ -6051,12 +6059,12 @@
         <f>IF(A127="crop", 0, G127)</f>
         <v>-0.30911111111111111</v>
       </c>
-      <c r="O127">
+      <c r="M127">
         <f t="shared" si="4"/>
-        <v>-8.7354800000000003E-4</v>
-      </c>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-8.7434285714285708E-4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>102</v>
       </c>
@@ -6064,7 +6072,7 @@
         <v>38</v>
       </c>
       <c r="C128">
-        <f>VLOOKUP(B128, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B128, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.16</v>
       </c>
       <c r="D128">
@@ -6075,7 +6083,7 @@
         <v>-7.008</v>
       </c>
       <c r="F128">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G128">
@@ -6090,12 +6098,12 @@
         <f>IF(A128="crop", 0, G128)</f>
         <v>-0.38933333333333331</v>
       </c>
-      <c r="O128">
+      <c r="M128">
         <f t="shared" si="4"/>
-        <v>-1.100256E-3</v>
-      </c>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.1012571428571426E-3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>102</v>
       </c>
@@ -6103,7 +6111,7 @@
         <v>39</v>
       </c>
       <c r="C129">
-        <f>VLOOKUP(B129, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B129, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.09</v>
       </c>
       <c r="D129">
@@ -6114,7 +6122,7 @@
         <v>-4.032</v>
       </c>
       <c r="F129">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G129">
@@ -6129,12 +6137,12 @@
         <f>IF(A129="crop", 0, G129)</f>
         <v>-0.224</v>
       </c>
-      <c r="O129">
-        <f>(H129*$L$11+I129*$M$11)*$N$11</f>
-        <v>-6.3302400000000004E-4</v>
-      </c>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M129">
+        <f>(H129*$J$11+I129*$K$11)*$L$11</f>
+        <v>-6.3360000000000001E-4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>102</v>
       </c>
@@ -6142,7 +6150,7 @@
         <v>40</v>
       </c>
       <c r="C130">
-        <f>VLOOKUP(B130, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B130, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D130">
@@ -6153,7 +6161,7 @@
         <v>0</v>
       </c>
       <c r="F130">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G130">
@@ -6168,12 +6176,12 @@
         <f>IF(A130="crop", 0, G130)</f>
         <v>0</v>
       </c>
-      <c r="O130">
-        <f t="shared" ref="O130:O158" si="6">(H130*$L$11+I130*$M$11)*$N$11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M130">
+        <f t="shared" ref="M130:M158" si="6">(H130*$J$11+I130*$K$11)*$L$11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>102</v>
       </c>
@@ -6181,7 +6189,7 @@
         <v>41</v>
       </c>
       <c r="C131">
-        <f>VLOOKUP(B131, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B131, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.04</v>
       </c>
       <c r="D131">
@@ -6192,7 +6200,7 @@
         <v>-1.8719999999999999</v>
       </c>
       <c r="F131">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G131">
@@ -6207,12 +6215,12 @@
         <f>IF(A131="crop", 0, G131)</f>
         <v>-0.104</v>
       </c>
-      <c r="O131">
+      <c r="M131">
         <f t="shared" si="6"/>
-        <v>-2.93904E-4</v>
-      </c>
-    </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-2.9417142857142854E-4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>102</v>
       </c>
@@ -6220,7 +6228,7 @@
         <v>42</v>
       </c>
       <c r="C132">
-        <f>VLOOKUP(B132, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B132, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.03</v>
       </c>
       <c r="D132">
@@ -6231,7 +6239,7 @@
         <v>-1.4339999999999999</v>
       </c>
       <c r="F132">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G132">
@@ -6246,12 +6254,12 @@
         <f>IF(A132="crop", 0, G132)</f>
         <v>-7.9666666666666663E-2</v>
       </c>
-      <c r="O132">
+      <c r="M132">
         <f t="shared" si="6"/>
-        <v>-2.25138E-4</v>
-      </c>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-2.2534285714285711E-4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>103</v>
       </c>
@@ -6259,7 +6267,7 @@
         <v>43</v>
       </c>
       <c r="C133">
-        <f>VLOOKUP(B133, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B133, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.14000000000000001</v>
       </c>
       <c r="D133">
@@ -6270,7 +6278,7 @@
         <v>-6.8319999999999999</v>
       </c>
       <c r="F133">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G133">
@@ -6285,12 +6293,12 @@
         <f>IF(A133="crop", 0, G133)</f>
         <v>-0.37955555555555553</v>
       </c>
-      <c r="O133">
+      <c r="M133">
         <f t="shared" si="6"/>
-        <v>-1.0726239999999999E-3</v>
-      </c>
-    </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.0735999999999999E-3</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>103</v>
       </c>
@@ -6298,7 +6306,7 @@
         <v>44</v>
       </c>
       <c r="C134">
-        <f>VLOOKUP(B134, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B134, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.31</v>
       </c>
       <c r="D134">
@@ -6309,7 +6317,7 @@
         <v>-15.437999999999999</v>
       </c>
       <c r="F134">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G134">
@@ -6324,12 +6332,12 @@
         <f>IF(A134="crop", 0, G134)</f>
         <v>-0.85766666666666658</v>
       </c>
-      <c r="O134">
+      <c r="M134">
         <f t="shared" si="6"/>
-        <v>-2.4237659999999999E-3</v>
-      </c>
-    </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-2.4259714285714282E-3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>103</v>
       </c>
@@ -6337,7 +6345,7 @@
         <v>45</v>
       </c>
       <c r="C135">
-        <f>VLOOKUP(B135, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B135, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.23</v>
       </c>
       <c r="D135">
@@ -6348,7 +6356,7 @@
         <v>-11.683999999999999</v>
       </c>
       <c r="F135">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G135">
@@ -6363,12 +6371,12 @@
         <f>IF(A135="crop", 0, G135)</f>
         <v>-0.64911111111111108</v>
       </c>
-      <c r="O135">
+      <c r="M135">
         <f t="shared" si="6"/>
-        <v>-1.8343880000000002E-3</v>
-      </c>
-    </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.8360571428571429E-3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>103</v>
       </c>
@@ -6376,7 +6384,7 @@
         <v>46</v>
       </c>
       <c r="C136">
-        <f>VLOOKUP(B136, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B136, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.17</v>
       </c>
       <c r="D136">
@@ -6387,7 +6395,7 @@
         <v>-8.8060000000000009</v>
       </c>
       <c r="F136">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G136">
@@ -6402,12 +6410,12 @@
         <f>IF(A136="crop", 0, G136)</f>
         <v>-0.48922222222222228</v>
       </c>
-      <c r="O136">
+      <c r="M136">
         <f t="shared" si="6"/>
-        <v>-1.3825420000000001E-3</v>
-      </c>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.3838000000000001E-3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>103</v>
       </c>
@@ -6415,7 +6423,7 @@
         <v>47</v>
       </c>
       <c r="C137">
-        <f>VLOOKUP(B137, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B137, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.17</v>
       </c>
       <c r="D137">
@@ -6426,7 +6434,7 @@
         <v>-8.9760000000000009</v>
       </c>
       <c r="F137">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G137">
@@ -6441,12 +6449,12 @@
         <f>IF(A137="crop", 0, G137)</f>
         <v>-0.4986666666666667</v>
       </c>
-      <c r="O137">
+      <c r="M137">
         <f t="shared" si="6"/>
-        <v>-1.4092320000000001E-3</v>
-      </c>
-    </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.4105142857142856E-3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>103</v>
       </c>
@@ -6454,7 +6462,7 @@
         <v>48</v>
       </c>
       <c r="C138">
-        <f>VLOOKUP(B138, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B138, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.08</v>
       </c>
       <c r="D138">
@@ -6465,7 +6473,7 @@
         <v>-4.3040000000000003</v>
       </c>
       <c r="F138">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G138">
@@ -6480,12 +6488,12 @@
         <f>IF(A138="crop", 0, G138)</f>
         <v>-0.23911111111111114</v>
       </c>
-      <c r="O138">
+      <c r="M138">
         <f t="shared" si="6"/>
-        <v>-6.7572800000000011E-4</v>
-      </c>
-    </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-6.7634285714285726E-4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>103</v>
       </c>
@@ -6493,7 +6501,7 @@
         <v>49</v>
       </c>
       <c r="C139">
-        <f>VLOOKUP(B139, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B139, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.11</v>
       </c>
       <c r="D139">
@@ -6504,7 +6512,7 @@
         <v>-6.0279999999999996</v>
       </c>
       <c r="F139">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G139">
@@ -6519,12 +6527,12 @@
         <f>IF(A139="crop", 0, G139)</f>
         <v>-0.33488888888888885</v>
       </c>
-      <c r="O139">
+      <c r="M139">
         <f t="shared" si="6"/>
-        <v>-9.4639599999999985E-4</v>
-      </c>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-9.4725714285714274E-4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>103</v>
       </c>
@@ -6532,7 +6540,7 @@
         <v>50</v>
       </c>
       <c r="C140">
-        <f>VLOOKUP(B140, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B140, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D140">
@@ -6543,7 +6551,7 @@
         <v>0</v>
       </c>
       <c r="F140">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G140">
@@ -6558,12 +6566,12 @@
         <f>IF(A140="crop", 0, G140)</f>
         <v>0</v>
       </c>
-      <c r="O140">
+      <c r="M140">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>103</v>
       </c>
@@ -6571,7 +6579,7 @@
         <v>51</v>
       </c>
       <c r="C141">
-        <f>VLOOKUP(B141, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B141, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.02</v>
       </c>
       <c r="D141">
@@ -6582,7 +6590,7 @@
         <v>-1.1359999999999999</v>
       </c>
       <c r="F141">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G141">
@@ -6597,12 +6605,12 @@
         <f>IF(A141="crop", 0, G141)</f>
         <v>-6.3111111111111104E-2</v>
       </c>
-      <c r="O141">
+      <c r="M141">
         <f t="shared" si="6"/>
-        <v>-1.7835199999999998E-4</v>
-      </c>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.7851428571428568E-4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>103</v>
       </c>
@@ -6610,7 +6618,7 @@
         <v>52</v>
       </c>
       <c r="C142">
-        <f>VLOOKUP(B142, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B142, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.08</v>
       </c>
       <c r="D142">
@@ -6621,7 +6629,7 @@
         <v>-4.6239999999999997</v>
       </c>
       <c r="F142">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G142">
@@ -6636,12 +6644,12 @@
         <f>IF(A142="crop", 0, G142)</f>
         <v>-0.25688888888888889</v>
       </c>
-      <c r="O142">
+      <c r="M142">
         <f t="shared" si="6"/>
-        <v>-7.2596800000000001E-4</v>
-      </c>
-    </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-7.2662857142857134E-4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>103</v>
       </c>
@@ -6649,7 +6657,7 @@
         <v>53</v>
       </c>
       <c r="C143">
-        <f>VLOOKUP(B143, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B143, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.06</v>
       </c>
       <c r="D143">
@@ -6660,7 +6668,7 @@
         <v>-3.5279999999999996</v>
       </c>
       <c r="F143">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G143">
@@ -6675,12 +6683,12 @@
         <f>IF(A143="crop", 0, G143)</f>
         <v>-0.19599999999999998</v>
       </c>
-      <c r="O143">
+      <c r="M143">
         <f t="shared" si="6"/>
-        <v>-5.538959999999999E-4</v>
-      </c>
-    </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-5.5439999999999992E-4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>103</v>
       </c>
@@ -6688,7 +6696,7 @@
         <v>54</v>
       </c>
       <c r="C144">
-        <f>VLOOKUP(B144, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B144, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.12</v>
       </c>
       <c r="D144">
@@ -6699,7 +6707,7 @@
         <v>-7.1759999999999993</v>
       </c>
       <c r="F144">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G144">
@@ -6714,12 +6722,12 @@
         <f>IF(A144="crop", 0, G144)</f>
         <v>-0.39866666666666661</v>
       </c>
-      <c r="O144">
+      <c r="M144">
         <f t="shared" si="6"/>
-        <v>-1.1266319999999998E-3</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.1276571428571426E-3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>103</v>
       </c>
@@ -6727,7 +6735,7 @@
         <v>55</v>
       </c>
       <c r="C145">
-        <f>VLOOKUP(B145, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B145, $Q$13:$R$96, 2, FALSE)</f>
         <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D145">
@@ -6738,7 +6746,7 @@
         <v>-4.2560000000000002</v>
       </c>
       <c r="F145">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G145">
@@ -6753,12 +6761,12 @@
         <f>IF(A145="crop", 0, G145)</f>
         <v>-0.23644444444444446</v>
       </c>
-      <c r="O145">
+      <c r="M145">
         <f t="shared" si="6"/>
-        <v>-6.6819199999999996E-4</v>
-      </c>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-6.6879999999999999E-4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>103</v>
       </c>
@@ -6766,7 +6774,7 @@
         <v>56</v>
       </c>
       <c r="C146">
-        <f>VLOOKUP(B146, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B146, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.13</v>
       </c>
       <c r="D146">
@@ -6777,7 +6785,7 @@
         <v>-8.0340000000000007</v>
       </c>
       <c r="F146">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G146">
@@ -6792,12 +6800,12 @@
         <f>IF(A146="crop", 0, G146)</f>
         <v>-0.44633333333333336</v>
       </c>
-      <c r="O146">
+      <c r="M146">
         <f t="shared" si="6"/>
-        <v>-1.2613380000000001E-3</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.2624857142857144E-3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>103</v>
       </c>
@@ -6805,7 +6813,7 @@
         <v>57</v>
       </c>
       <c r="C147">
-        <f>VLOOKUP(B147, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B147, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D147">
@@ -6816,7 +6824,7 @@
         <v>0</v>
       </c>
       <c r="F147">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G147">
@@ -6831,12 +6839,12 @@
         <f>IF(A147="crop", 0, G147)</f>
         <v>0</v>
       </c>
-      <c r="O147">
+      <c r="M147">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>103</v>
       </c>
@@ -6844,7 +6852,7 @@
         <v>58</v>
       </c>
       <c r="C148">
-        <f>VLOOKUP(B148, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B148, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.24</v>
       </c>
       <c r="D148">
@@ -6855,7 +6863,7 @@
         <v>-15.311999999999999</v>
       </c>
       <c r="F148">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G148">
@@ -6870,12 +6878,12 @@
         <f>IF(A148="crop", 0, G148)</f>
         <v>-0.85066666666666668</v>
       </c>
-      <c r="O148">
+      <c r="M148">
         <f t="shared" si="6"/>
-        <v>-2.4039840000000001E-3</v>
-      </c>
-    </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-2.4061714285714283E-3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>103</v>
       </c>
@@ -6883,7 +6891,7 @@
         <v>59</v>
       </c>
       <c r="C149">
-        <f>VLOOKUP(B149, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B149, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.32</v>
       </c>
       <c r="D149">
@@ -6894,7 +6902,7 @@
         <v>-20.736000000000001</v>
       </c>
       <c r="F149">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G149">
@@ -6909,12 +6917,12 @@
         <f>IF(A149="crop", 0, G149)</f>
         <v>-1.1520000000000001</v>
       </c>
-      <c r="O149">
+      <c r="M149">
         <f t="shared" si="6"/>
-        <v>-3.2555520000000001E-3</v>
-      </c>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-3.2585142857142857E-3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>103</v>
       </c>
@@ -6922,7 +6930,7 @@
         <v>60</v>
       </c>
       <c r="C150">
-        <f>VLOOKUP(B150, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B150, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D150">
@@ -6933,7 +6941,7 @@
         <v>0</v>
       </c>
       <c r="F150">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G150">
@@ -6948,12 +6956,12 @@
         <f>IF(A150="crop", 0, G150)</f>
         <v>0</v>
       </c>
-      <c r="O150">
+      <c r="M150">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>103</v>
       </c>
@@ -6961,7 +6969,7 @@
         <v>61</v>
       </c>
       <c r="C151">
-        <f>VLOOKUP(B151, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B151, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D151">
@@ -6972,7 +6980,7 @@
         <v>0</v>
       </c>
       <c r="F151">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G151">
@@ -6987,12 +6995,12 @@
         <f>IF(A151="crop", 0, G151)</f>
         <v>0</v>
       </c>
-      <c r="O151">
+      <c r="M151">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>103</v>
       </c>
@@ -7000,7 +7008,7 @@
         <v>62</v>
       </c>
       <c r="C152">
-        <f>VLOOKUP(B152, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B152, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.1</v>
       </c>
       <c r="D152">
@@ -7011,7 +7019,7 @@
         <v>-6.78</v>
       </c>
       <c r="F152">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G152">
@@ -7026,12 +7034,12 @@
         <f>IF(A152="crop", 0, G152)</f>
         <v>-0.37666666666666671</v>
       </c>
-      <c r="O152">
+      <c r="M152">
         <f t="shared" si="6"/>
-        <v>-1.0644600000000001E-3</v>
-      </c>
-    </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.0654285714285713E-3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>103</v>
       </c>
@@ -7039,7 +7047,7 @@
         <v>63</v>
       </c>
       <c r="C153">
-        <f>VLOOKUP(B153, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B153, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.33</v>
       </c>
       <c r="D153">
@@ -7050,7 +7058,7 @@
         <v>-22.704000000000001</v>
       </c>
       <c r="F153">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G153">
@@ -7065,12 +7073,12 @@
         <f>IF(A153="crop", 0, G153)</f>
         <v>-1.2613333333333334</v>
       </c>
-      <c r="O153">
+      <c r="M153">
         <f t="shared" si="6"/>
-        <v>-3.5645280000000004E-3</v>
-      </c>
-    </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-3.5677714285714287E-3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>103</v>
       </c>
@@ -7078,7 +7086,7 @@
         <v>64</v>
       </c>
       <c r="C154">
-        <f>VLOOKUP(B154, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B154, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D154">
@@ -7089,7 +7097,7 @@
         <v>0</v>
       </c>
       <c r="F154">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G154">
@@ -7104,12 +7112,12 @@
         <f>IF(A154="crop", 0, G154)</f>
         <v>0</v>
       </c>
-      <c r="O154">
+      <c r="M154">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>103</v>
       </c>
@@ -7117,7 +7125,7 @@
         <v>65</v>
       </c>
       <c r="C155">
-        <f>VLOOKUP(B155, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B155, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.05</v>
       </c>
       <c r="D155">
@@ -7128,7 +7136,7 @@
         <v>-3.54</v>
       </c>
       <c r="F155">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G155">
@@ -7143,12 +7151,12 @@
         <f>IF(A155="crop", 0, G155)</f>
         <v>-0.19666666666666666</v>
       </c>
-      <c r="O155">
+      <c r="M155">
         <f t="shared" si="6"/>
-        <v>-5.5577999999999997E-4</v>
-      </c>
-    </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-5.5628571428571424E-4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>103</v>
       </c>
@@ -7156,7 +7164,7 @@
         <v>66</v>
       </c>
       <c r="C156">
-        <f>VLOOKUP(B156, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B156, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.26</v>
       </c>
       <c r="D156">
@@ -7167,7 +7175,7 @@
         <v>-18.667999999999999</v>
       </c>
       <c r="F156">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G156">
@@ -7182,12 +7190,12 @@
         <f>IF(A156="crop", 0, G156)</f>
         <v>-1.0371111111111111</v>
       </c>
-      <c r="O156">
+      <c r="M156">
         <f t="shared" si="6"/>
-        <v>-2.9308759999999998E-3</v>
-      </c>
-    </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-2.933542857142857E-3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>103</v>
       </c>
@@ -7195,7 +7203,7 @@
         <v>67</v>
       </c>
       <c r="C157">
-        <f>VLOOKUP(B157, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B157, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.26</v>
       </c>
       <c r="D157">
@@ -7206,7 +7214,7 @@
         <v>-18.928000000000001</v>
       </c>
       <c r="F157">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G157">
@@ -7221,12 +7229,12 @@
         <f>IF(A157="crop", 0, G157)</f>
         <v>-1.0515555555555556</v>
       </c>
-      <c r="O157">
+      <c r="M157">
         <f t="shared" si="6"/>
-        <v>-2.9716960000000002E-3</v>
-      </c>
-    </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-2.9743999999999999E-3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>103</v>
       </c>
@@ -7234,7 +7242,7 @@
         <v>68</v>
       </c>
       <c r="C158">
-        <f>VLOOKUP(B158, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B158, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.03</v>
       </c>
       <c r="D158">
@@ -7245,7 +7253,7 @@
         <v>-2.214</v>
       </c>
       <c r="F158">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G158">
@@ -7260,12 +7268,12 @@
         <f>IF(A158="crop", 0, G158)</f>
         <v>-0.123</v>
       </c>
-      <c r="O158">
+      <c r="M158">
         <f t="shared" si="6"/>
-        <v>-3.4759800000000002E-4</v>
-      </c>
-    </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-3.4791428571428568E-4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>103</v>
       </c>
@@ -7273,7 +7281,7 @@
         <v>69</v>
       </c>
       <c r="C159">
-        <f>VLOOKUP(B159, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B159, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.37</v>
       </c>
       <c r="D159">
@@ -7284,7 +7292,7 @@
         <v>-27.675999999999998</v>
       </c>
       <c r="F159">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G159">
@@ -7299,12 +7307,12 @@
         <f>IF(A159="crop", 0, G159)</f>
         <v>-1.5375555555555556</v>
       </c>
-      <c r="O159">
-        <f>(H159*$L$11+I159*$M$11)*$N$11</f>
-        <v>-4.3451319999999998E-3</v>
-      </c>
-    </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M159">
+        <f>(H159*$J$11+I159*$K$11)*$L$11</f>
+        <v>-4.3490857142857138E-3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>103</v>
       </c>
@@ -7312,7 +7320,7 @@
         <v>70</v>
       </c>
       <c r="C160">
-        <f>VLOOKUP(B160, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B160, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.01</v>
       </c>
       <c r="D160">
@@ -7323,7 +7331,7 @@
         <v>-0.75800000000000001</v>
       </c>
       <c r="F160">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G160">
@@ -7338,12 +7346,12 @@
         <f>IF(A160="crop", 0, G160)</f>
         <v>-4.2111111111111113E-2</v>
       </c>
-      <c r="O160">
-        <f t="shared" ref="O160:O178" si="8">(H160*$L$11+I160*$M$11)*$N$11</f>
-        <v>-1.1900600000000001E-4</v>
-      </c>
-    </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M160">
+        <f t="shared" ref="M160:M178" si="8">(H160*$J$11+I160*$K$11)*$L$11</f>
+        <v>-1.1911428571428571E-4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>103</v>
       </c>
@@ -7351,7 +7359,7 @@
         <v>71</v>
       </c>
       <c r="C161">
-        <f>VLOOKUP(B161, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B161, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.03</v>
       </c>
       <c r="D161">
@@ -7362,7 +7370,7 @@
         <v>-2.3039999999999998</v>
       </c>
       <c r="F161">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G161">
@@ -7377,12 +7385,12 @@
         <f>IF(A161="crop", 0, G161)</f>
         <v>-0.128</v>
       </c>
-      <c r="O161">
+      <c r="M161">
         <f t="shared" si="8"/>
-        <v>-3.6172800000000002E-4</v>
-      </c>
-    </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-3.6205714285714283E-4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>103</v>
       </c>
@@ -7390,7 +7398,7 @@
         <v>72</v>
       </c>
       <c r="C162">
-        <f>VLOOKUP(B162, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B162, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.1</v>
       </c>
       <c r="D162">
@@ -7401,7 +7409,7 @@
         <v>-7.78</v>
       </c>
       <c r="F162">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G162">
@@ -7416,12 +7424,12 @@
         <f>IF(A162="crop", 0, G162)</f>
         <v>-0.43222222222222223</v>
       </c>
-      <c r="O162">
+      <c r="M162">
         <f t="shared" si="8"/>
-        <v>-1.2214600000000002E-3</v>
-      </c>
-    </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.2225714285714286E-3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>103</v>
       </c>
@@ -7429,7 +7437,7 @@
         <v>73</v>
       </c>
       <c r="C163">
-        <f>VLOOKUP(B163, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B163, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.25</v>
       </c>
       <c r="D163">
@@ -7440,7 +7448,7 @@
         <v>-19.7</v>
       </c>
       <c r="F163">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G163">
@@ -7455,12 +7463,12 @@
         <f>IF(A163="crop", 0, G163)</f>
         <v>-1.0944444444444443</v>
       </c>
-      <c r="O163">
+      <c r="M163">
         <f t="shared" si="8"/>
-        <v>-3.0928999999999996E-3</v>
-      </c>
-    </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-3.095714285714285E-3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>103</v>
       </c>
@@ -7468,7 +7476,7 @@
         <v>74</v>
       </c>
       <c r="C164">
-        <f>VLOOKUP(B164, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B164, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.27</v>
       </c>
       <c r="D164">
@@ -7479,7 +7487,7 @@
         <v>-21.545999999999999</v>
       </c>
       <c r="F164">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G164">
@@ -7494,12 +7502,12 @@
         <f>IF(A164="crop", 0, G164)</f>
         <v>-1.1970000000000001</v>
       </c>
-      <c r="O164">
+      <c r="M164">
         <f t="shared" si="8"/>
-        <v>-3.3827220000000003E-3</v>
-      </c>
-    </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-3.3858E-3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>103</v>
       </c>
@@ -7507,7 +7515,7 @@
         <v>75</v>
       </c>
       <c r="C165">
-        <f>VLOOKUP(B165, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B165, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.18</v>
       </c>
       <c r="D165">
@@ -7518,7 +7526,7 @@
         <v>-14.543999999999999</v>
       </c>
       <c r="F165">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G165">
@@ -7533,12 +7541,12 @@
         <f>IF(A165="crop", 0, G165)</f>
         <v>-0.80799999999999994</v>
       </c>
-      <c r="O165">
+      <c r="M165">
         <f t="shared" si="8"/>
-        <v>-2.2834079999999998E-3</v>
-      </c>
-    </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-2.2854857142857138E-3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>103</v>
       </c>
@@ -7546,7 +7554,7 @@
         <v>76</v>
       </c>
       <c r="C166">
-        <f>VLOOKUP(B166, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B166, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.12</v>
       </c>
       <c r="D166">
@@ -7557,7 +7565,7 @@
         <v>-9.8159999999999989</v>
       </c>
       <c r="F166">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G166">
@@ -7572,12 +7580,12 @@
         <f>IF(A166="crop", 0, G166)</f>
         <v>-0.54533333333333323</v>
       </c>
-      <c r="O166">
+      <c r="M166">
         <f t="shared" si="8"/>
-        <v>-1.5411119999999996E-3</v>
-      </c>
-    </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-1.5425142857142854E-3</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>103</v>
       </c>
@@ -7585,7 +7593,7 @@
         <v>77</v>
       </c>
       <c r="C167">
-        <f>VLOOKUP(B167, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B167, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.22</v>
       </c>
       <c r="D167">
@@ -7596,7 +7604,7 @@
         <v>-18.216000000000001</v>
       </c>
       <c r="F167">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G167">
@@ -7611,12 +7619,12 @@
         <f>IF(A167="crop", 0, G167)</f>
         <v>-1.012</v>
       </c>
-      <c r="O167">
+      <c r="M167">
         <f t="shared" si="8"/>
-        <v>-2.859912E-3</v>
-      </c>
-    </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-2.8625142857142856E-3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>103</v>
       </c>
@@ -7624,7 +7632,7 @@
         <v>78</v>
       </c>
       <c r="C168">
-        <f>VLOOKUP(B168, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B168, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.2</v>
       </c>
       <c r="D168">
@@ -7635,7 +7643,7 @@
         <v>-16.760000000000002</v>
       </c>
       <c r="F168">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G168">
@@ -7650,12 +7658,12 @@
         <f>IF(A168="crop", 0, G168)</f>
         <v>-0.93111111111111122</v>
       </c>
-      <c r="O168">
+      <c r="M168">
         <f t="shared" si="8"/>
-        <v>-2.6313200000000004E-3</v>
-      </c>
-    </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-2.6337142857142861E-3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>103</v>
       </c>
@@ -7663,7 +7671,7 @@
         <v>79</v>
       </c>
       <c r="C169">
-        <f>VLOOKUP(B169, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B169, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.18</v>
       </c>
       <c r="D169">
@@ -7674,7 +7682,7 @@
         <v>-15.263999999999999</v>
       </c>
       <c r="F169">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G169">
@@ -7689,12 +7697,12 @@
         <f>IF(A169="crop", 0, G169)</f>
         <v>-0.84799999999999998</v>
       </c>
-      <c r="O169">
+      <c r="M169">
         <f t="shared" si="8"/>
-        <v>-2.3964480000000002E-3</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-2.3986285714285714E-3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>103</v>
       </c>
@@ -7702,7 +7710,7 @@
         <v>80</v>
       </c>
       <c r="C170">
-        <f>VLOOKUP(B170, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B170, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.4</v>
       </c>
       <c r="D170">
@@ -7713,7 +7721,7 @@
         <v>-34.32</v>
       </c>
       <c r="F170">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G170">
@@ -7728,12 +7736,12 @@
         <f>IF(A170="crop", 0, G170)</f>
         <v>-1.9066666666666667</v>
       </c>
-      <c r="O170">
+      <c r="M170">
         <f t="shared" si="8"/>
-        <v>-5.3882400000000007E-3</v>
-      </c>
-    </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-5.3931428571428576E-3</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>103</v>
       </c>
@@ -7741,7 +7749,7 @@
         <v>81</v>
       </c>
       <c r="C171">
-        <f>VLOOKUP(B171, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B171, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.21</v>
       </c>
       <c r="D171">
@@ -7752,7 +7760,7 @@
         <v>-18.227999999999998</v>
       </c>
       <c r="F171">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G171">
@@ -7767,12 +7775,12 @@
         <f>IF(A171="crop", 0, G171)</f>
         <v>-1.0126666666666666</v>
       </c>
-      <c r="O171">
+      <c r="M171">
         <f t="shared" si="8"/>
-        <v>-2.8617959999999998E-3</v>
-      </c>
-    </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-2.8643999999999996E-3</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>103</v>
       </c>
@@ -7780,7 +7788,7 @@
         <v>82</v>
       </c>
       <c r="C172">
-        <f>VLOOKUP(B172, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B172, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.39</v>
       </c>
       <c r="D172">
@@ -7791,7 +7799,7 @@
         <v>-34.241999999999997</v>
       </c>
       <c r="F172">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G172">
@@ -7806,12 +7814,12 @@
         <f>IF(A172="crop", 0, G172)</f>
         <v>-1.9023333333333332</v>
       </c>
-      <c r="O172">
+      <c r="M172">
         <f t="shared" si="8"/>
-        <v>-5.3759939999999994E-3</v>
-      </c>
-    </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-5.3808857142857132E-3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>103</v>
       </c>
@@ -7819,7 +7827,7 @@
         <v>83</v>
       </c>
       <c r="C173">
-        <f>VLOOKUP(B173, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B173, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.69</v>
       </c>
       <c r="D173">
@@ -7830,7 +7838,7 @@
         <v>-61.271999999999991</v>
       </c>
       <c r="F173">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G173">
@@ -7845,12 +7853,12 @@
         <f>IF(A173="crop", 0, G173)</f>
         <v>-3.4039999999999995</v>
       </c>
-      <c r="O173">
+      <c r="M173">
         <f t="shared" si="8"/>
-        <v>-9.619703999999998E-3</v>
-      </c>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-9.628457142857141E-3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>103</v>
       </c>
@@ -7858,7 +7866,7 @@
         <v>84</v>
       </c>
       <c r="C174">
-        <f>VLOOKUP(B174, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B174, $Q$13:$R$96, 2, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D174">
@@ -7869,7 +7877,7 @@
         <v>0</v>
       </c>
       <c r="F174">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G174">
@@ -7884,12 +7892,12 @@
         <f>IF(A174="crop", 0, G174)</f>
         <v>0</v>
       </c>
-      <c r="O174">
+      <c r="M174">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>103</v>
       </c>
@@ -7897,7 +7905,7 @@
         <v>85</v>
       </c>
       <c r="C175">
-        <f>VLOOKUP(B175, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B175, $Q$13:$R$96, 2, FALSE)</f>
         <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D175">
@@ -7908,7 +7916,7 @@
         <v>-6.3560000000000008</v>
       </c>
       <c r="F175">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G175">
@@ -7923,12 +7931,12 @@
         <f>IF(A175="crop", 0, G175)</f>
         <v>-0.35311111111111115</v>
       </c>
-      <c r="O175">
+      <c r="M175">
         <f t="shared" si="8"/>
-        <v>-9.9789200000000022E-4</v>
-      </c>
-    </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-9.9879999999999999E-4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>103</v>
       </c>
@@ -7936,7 +7944,7 @@
         <v>86</v>
       </c>
       <c r="C176">
-        <f>VLOOKUP(B176, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B176, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.56999999999999995</v>
       </c>
       <c r="D176">
@@ -7947,7 +7955,7 @@
         <v>-52.325999999999993</v>
       </c>
       <c r="F176">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G176">
@@ -7962,12 +7970,12 @@
         <f>IF(A176="crop", 0, G176)</f>
         <v>-2.9069999999999996</v>
       </c>
-      <c r="O176">
+      <c r="M176">
         <f t="shared" si="8"/>
-        <v>-8.215181999999998E-3</v>
-      </c>
-    </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-8.2226571428571406E-3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>103</v>
       </c>
@@ -7975,7 +7983,7 @@
         <v>87</v>
       </c>
       <c r="C177">
-        <f>VLOOKUP(B177, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B177, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.67</v>
       </c>
       <c r="D177">
@@ -7986,7 +7994,7 @@
         <v>-62.176000000000002</v>
       </c>
       <c r="F177">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G177">
@@ -8001,12 +8009,12 @@
         <f>IF(A177="crop", 0, G177)</f>
         <v>-3.4542222222222225</v>
       </c>
-      <c r="O177">
+      <c r="M177">
         <f t="shared" si="8"/>
-        <v>-9.761632000000001E-3</v>
-      </c>
-    </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.2">
+        <v>-9.7705142857142865E-3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>103</v>
       </c>
@@ -8014,7 +8022,7 @@
         <v>88</v>
       </c>
       <c r="C178">
-        <f>VLOOKUP(B178, $S$13:$T$96, 2, FALSE)</f>
+        <f>VLOOKUP(B178, $Q$13:$R$96, 2, FALSE)</f>
         <v>-0.05</v>
       </c>
       <c r="D178">
@@ -8025,7 +8033,7 @@
         <v>-4.6900000000000004</v>
       </c>
       <c r="F178">
-        <f>$R$6</f>
+        <f>$P$6</f>
         <v>18</v>
       </c>
       <c r="G178">
@@ -8040,9 +8048,9 @@
         <f>IF(A178="crop", 0, G178)</f>
         <v>-0.2605555555555556</v>
       </c>
-      <c r="O178">
+      <c r="M178">
         <f t="shared" si="8"/>
-        <v>-7.363300000000001E-4</v>
+        <v>-7.3700000000000013E-4</v>
       </c>
     </row>
   </sheetData>
